--- a/data/codal_disclosures_latest.xlsx
+++ b/data/codal_disclosures_latest.xlsx
@@ -19,12 +19,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'اطلاعیه‌ها'!$A$1:$L$165</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'طرح‌های توسعه'!$A$1:$L$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'صورت‌های مالی'!$A$1:$L$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'طرح‌های توسعه'!$A$1:$L$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'صورت‌های مالی'!$A$1:$L$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'پست‌های تلگرام'!$A$1:$G$161</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'فهرست نمادها'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'پیوست‌های اکسل'!$A$1:$J$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'وضعیت منابع'!$A$1:$G$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'پیوست‌های اکسل'!$A$1:$J$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'وضعیت منابع'!$A$1:$G$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -480,7 +480,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T13:23:21+00:00</t>
+          <t>2026-10-13T13:27:49+00:00</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -599,12 +599,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>حداکثر 8 پیوست در هر اجرا</t>
+          <t>حداکثر 3 پیوست در هر اجرا</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
@@ -839,19 +839,15 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>صورت‌های مالی/حسابرسی</t>
+          <t>نیازمند دسته‌بندی دستی</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>صورت های مالی؛ صورت‌های مالی</t>
-        </is>
-      </c>
+      <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>3 پاسا ایران یاسا تایر و رابر لینک سابقه معاملات پاسا ریز معاملات امروز پاسا سهامداران عمده پاسا افزایش سرمایه پاسا تعدیل قیمت پاسا تابلو عرضه و تقاضا صورتهای مالی نسبتهای مالی رتبه بندی بنیادی پاسا اندیکاتورها پاسا در TSETMC پاسا در کدال مشخصات کمیته ریسک</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پاسا 🏛️ ایران یاسا تایر و رابر 📋 مشخصات کمیته ریسک 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۳۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 4 views 13:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -878,7 +874,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>توقف نماد معاملاتی ناشر به استناد ماده ۱۹ مکرر/ ۱۲ مکرر ۳دستورالعمل اجرایی نحوه انجام معاملات</t>
+          <t>لینک اطلاعیه</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -893,19 +889,15 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>صورت‌های مالی/حسابرسی</t>
+          <t>نیازمند دسته‌بندی دستی</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>صورت های مالی؛ صورت‌های مالی</t>
-        </is>
-      </c>
+      <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5 ولملت واسپاری ملت لینک سابقه معاملات ولملت ریز معاملات امروز ولملت سهامداران عمده ولملت افزایش سرمایه ولملت تعدیل قیمت ولملت تابلو عرضه و تقاضا صورتهای مالی نسبتهای مالی رتبه بندی بنیادی ولملت اندیکاتورها ولملت در TSETMC ولملت در کدال توقف نماد معاملاتی ناشر به استناد ماده ۱۹ مکرر/ ۱۲ مکرر ۳دستورالعمل اجرایی نحوه انجام معاملات</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ولملت 🏛️ واسپاری ملت 📋 توقف نماد معاملاتی ناشر به استناد ماده ۱۹ مکرر/ ۱۲ مکرر ۳دستورالعمل اجرایی نحوه انجام معاملات 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۲:۳۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 5 views 13:15 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -915,12 +907,12 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>بورس‌تریدر؛ تلگرام بورس‌تریدر</t>
+          <t>تلگرام بورس‌تریدر</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://bourse-trader.ir/index.php?task=codal-reports؛ https://t.me/codalboursetrader/247762</t>
+          <t>https://t.me/codalboursetrader/247762</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1509,7 @@
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #غدشت 🏛️ فرآورده های غذایی دشت مرغاب 📌 #خلاصه_تصمیمات_مجمع_عمومی_عادی_سالیانه 📋 خلاصه تصمیمات مجمع عمومی فوق العاده دوره ۱۲ ماهه منتهی به ۱۴۰۶/۰۳/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۱۶:۱۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 11 views 12:48 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #غدشت 🏛️ فرآورده های غذایی دشت مرغاب 📌 #خلاصه_تصمیمات_مجمع_عمومی_عادی_سالیانه 📋 خلاصه تصمیمات مجمع عمومی فوق العاده دوره ۱۲ ماهه منتهی به ۱۴۰۶/۰۳/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۱۶:۱۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 12:48 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1567,7 +1559,7 @@
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آرمان_اندیش_بازار 🏛️ صندوق اختصاصی بازارگردانی آرمان اندیش 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۱۰:۱۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 12:42 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آرمان_اندیش_بازار 🏛️ صندوق اختصاصی بازارگردانی آرمان اندیش 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۱۰:۱۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 14 views 12:42 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1617,7 +1609,7 @@
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #خیمن 🏛️ ایمن خودرو شرق 📌 #لغو_آگهی_ (اطلاعیه)_دعوت_به_مجمع_عمومی 📋 لغو آگهی (اطلاعیه) دعوت به مجمع عمومی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۰۹:۳۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 12:42 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #خیمن 🏛️ ایمن خودرو شرق 📌 #لغو_آگهی_ (اطلاعیه)_دعوت_به_مجمع_عمومی 📋 لغو آگهی (اطلاعیه) دعوت به مجمع عمومی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۰۹:۳۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 12:42 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1649,17 +1641,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>غدشت</t>
+          <t>خکار</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:39:05+00:00</t>
+          <t>2026-10-13T12:33:07+00:00</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>نیازمند دسته‌بندی دستی</t>
+          <t>افزایش سرمایه</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
@@ -1667,12 +1659,12 @@
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #غدشت 🏛️ فرآورده های غذایی دشت مرغاب 📌 #خلاصه_تصمیمات_مجمع_عمومی_عادی_سالیانه 📋 خلاصه تصمیمات مجمع عمومی عادی سالیانه دوره ۱۲ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۰۷:۵۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 12:39 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #خکار 🏛️ ایرکا پارت صنعت 📌 #پیشنهاد_هیئت_مدیره_به_مجمع_عمومی_فوق_العاده_در_خصوص_افزایش_سرمایه 📋 پیشنهاد هیئت مدیره به مجمع عمومی فوق العاده در خصوص افزایش سرمایه 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۰۱:۰۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 12:33 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=5MR5Q0tugykfutUJ38wrOQ%3d%3d&amp;rt=0&amp;let=2020&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=6gcOJPWETQDFOgRL2C9nXg%3d%3d&amp;rt=0&amp;let=55&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1682,7 +1674,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247747</t>
+          <t>https://t.me/codalboursetrader/247746</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1859,7 @@
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سفارس 🏛️ سیمان فارس و خوزستان 📌 #آگهی_ثبت_تصمیمات_مجمع_عادی_سالیانه 📋 آگهی ثبت تصمیمات مجمع عادی سالیانه دوره ۱۲ ماهه منتهی به ۱۴۰۵/۰۲/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۵۱:۰۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 16 views 12:21 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سفارس 🏛️ سیمان فارس و خوزستان 📌 #آگهی_ثبت_تصمیمات_مجمع_عادی_سالیانه 📋 آگهی ثبت تصمیمات مجمع عادی سالیانه دوره ۱۲ ماهه منتهی به ۱۴۰۵/۰۲/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۵۱:۰۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 12:21 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1917,7 +1909,7 @@
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #غچین 🏛️ مجتمع کشت و صنعت چین چین 📌 #گزارش_کنترل_داخلی 📋 گزارش کنترل های داخلی در تاریخ ۱۴۰۵/۰۳/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۴۹:۴۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 16 views 12:21 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #غچین 🏛️ مجتمع کشت و صنعت چین چین 📌 #گزارش_کنترل_داخلی 📋 گزارش کنترل های داخلی در تاریخ ۱۴۰۵/۰۳/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۴۹:۴۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 12:21 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1967,7 +1959,7 @@
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #بکابل 🏛️ سیم و کابل ابهر 📌 #پیشنهاد_هیئت_مدیره_به_مجمع_عمومی_فوق_العاده_در_خصوص_افزایش_سرمایه 📋 پیشنهاد هیئت مدیره به مجمع عمومی فوق العاده در خصوص افزایش سرمایه 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۴۵:۱۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 12:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #بکابل 🏛️ سیم و کابل ابهر 📌 #پیشنهاد_هیئت_مدیره_به_مجمع_عمومی_فوق_العاده_در_خصوص_افزایش_سرمایه 📋 پیشنهاد هیئت مدیره به مجمع عمومی فوق العاده در خصوص افزایش سرمایه 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۴۵:۱۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 14 views 12:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2017,7 +2009,7 @@
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تکیمیا 🏛️ تامین سرمایه کیمیا 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - تعهد پذیره نویسی و بازارگردانی اوراق دایو پارس- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۴۴:۵۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 12:15 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تکیمیا 🏛️ تامین سرمایه کیمیا 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - تعهد پذیره نویسی و بازارگردانی اوراق دایو پارس- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۴۴:۵۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 12:15 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2071,7 +2063,7 @@
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ثنا 🏛️ زرین نهال ثنا 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۴۲:۰۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 16 views 12:15 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ثنا 🏛️ زرین نهال ثنا 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۴۲:۰۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 12:15 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2275,7 +2267,7 @@
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شپترو 🏛️ پتروشیمی آبادان 📋 مشخصات کمیته ریسک 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۳۵:۱۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 12:06 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شپترو 🏛️ پتروشیمی آبادان 📋 مشخصات کمیته ریسک 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۳۵:۱۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 12:06 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2325,7 +2317,7 @@
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #حافظ_سهام 🏛️ صندوق سرمایه گذاری مشترک کارگزاری حافظ 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۳۴:۴۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 12:06 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #حافظ_سهام 🏛️ صندوق سرمایه گذاری مشترک کارگزاری حافظ 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۳۴:۴۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 12:06 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2429,7 +2421,7 @@
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #واعتماد 🏛️ سرمایه گذاری توسعه اعتماد 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ (حسابرسی نشده)(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۲۲:۳۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 8 views 11:54 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #واعتماد 🏛️ سرمایه گذاری توسعه اعتماد 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ (حسابرسی نشده)(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۲۲:۳۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 9 views 11:54 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2479,7 +2471,7 @@
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #حافظ_سهام 🏛️ صندوق سرمایه گذاری مشترک کارگزاری حافظ 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۲۲:۰۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 8 views 11:54 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #حافظ_سهام 🏛️ صندوق سرمایه گذاری مشترک کارگزاری حافظ 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۲۲:۰۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 9 views 11:54 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2661,30 +2653,34 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>پیمان</t>
+          <t>کی ام سی</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:36:04+00:00</t>
+          <t>2026-10-13T11:30:09+00:00</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>نیازمند دسته‌بندی دستی</t>
+          <t>صورت‌های مالی/حسابرسی</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>صورت های مالی؛ صورت‌های مالی؛ گزارش فعالیت ماهانه؛ فعالیت ماهانه</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📋 کمیته انتصابات 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۰۳:۵۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 14 views 11:36 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کی_ام_سی 🏛️ کرمان موتور 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۴/۰۷/۳۰ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۵۹:۳۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 14 views 11:30 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=u1AHqlYmb3oC5SoeP0X3jw%3d%3d&amp;rt=5&amp;let=248&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=aoCafEWSkkL36C63gVbsWQ%3d%3d&amp;rt=0&amp;let=58&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2694,7 +2690,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247726</t>
+          <t>https://t.me/codalboursetrader/247725</t>
         </is>
       </c>
     </row>
@@ -3689,34 +3685,30 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>تبرک</t>
+          <t>بیوتیک</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:42:06+00:00</t>
+          <t>2026-10-13T10:42:05+00:00</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>طرح توسعه/پروژه</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>بهره برداری؛ بهره‌برداری</t>
-        </is>
-      </c>
+          <t>نیازمند دسته‌بندی دستی</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تبرک 🏛️ گروه کارخانجات صنعتی تبرک 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - اجازه بهره برداری- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۰۹:۵۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 21 views 10:42 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #بیوتیک 🏛️ آنتی بیوتیک سازی ایران 📌 #معرفی /تغییر_در_ترکیب_اعضای_هیئت _مدیره 📋 معرفی /تغییر در ترکیب اعضای هیئت مدیره/مدیر عامل(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۰۹:۲۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 20 views 10:42 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=5XQQQaQQQKiXjQjKpTJ7Ei9Op6HA%3d%3d&amp;rt=2&amp;let=11&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=IouUliviWwmYAA0Cq7dDdg%3d%3d&amp;rt=0&amp;let=19&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3726,7 +3718,7 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247705</t>
+          <t>https://t.me/codalboursetrader/247704</t>
         </is>
       </c>
     </row>
@@ -4721,12 +4713,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>کاریزما ثابت</t>
+          <t>ره آورد ثابت</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T09:42:05+00:00</t>
+          <t>2026-10-13T09:39:05+00:00</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4739,12 +4731,12 @@
       <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کاریزما_ثابت 🏛️ در اوراق بهادار با درآمد ثابت کاریزما 📋 تصمیمات مجمع صندوق سرمایه گذاری(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۱۱:۰۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 09:42 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ره_آورد_ثابت 🏛️ ره آورد آباد مسکن 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۷/۲۲ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۰۸:۴۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 28 views 09:39 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=21ZvucWY6fuHJ3h2yLgXQQQaQQQA%3d%3d&amp;rt=2&amp;let=122&amp;ct=5&amp;ft=2</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=E6OOObOOO2u34ku5keWWAMq88MDg%3d%3d&amp;rt=2&amp;let=121&amp;ct=5&amp;ft=2</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4754,7 +4746,7 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247684</t>
+          <t>https://t.me/codalboursetrader/247683</t>
         </is>
       </c>
     </row>
@@ -5733,30 +5725,34 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>رابین بازار</t>
+          <t>کسعدی</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T08:09:07+00:00</t>
+          <t>2026-10-13T08:00:13+00:00</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>نیازمند دسته‌بندی دستی</t>
+          <t>صورت‌های مالی/حسابرسی</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr"/>
-      <c r="G99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>صورت های مالی؛ صورت‌های مالی؛ گزارش فعالیت ماهانه؛ فعالیت ماهانه</t>
+        </is>
+      </c>
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #رابین_بازار 🏛️ اختصاصی بازارگردانی رابین سهم 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۳ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۳۶:۵۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 14 views 08:09 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کسعدی 🏛️ کارخانجات کاشی و سرامیک سعدی 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۲۷:۴۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 16 views 08:00 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=6cAOOObOOOmdsnQQQaQQQJsfgsQQQaQQQEKwCATw%3d%3d&amp;rt=2&amp;let=121&amp;ct=5&amp;ft=7</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=163NzE0XtsLfeG4Va20D3A%3d%3d&amp;rt=0&amp;let=58&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -5766,7 +5762,7 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247663</t>
+          <t>https://t.me/codalboursetrader/247662</t>
         </is>
       </c>
     </row>
@@ -6741,12 +6737,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>آواک</t>
+          <t>غنیلی</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T06:33:08+00:00</t>
+          <t>2026-10-13T06:27:04+00:00</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6759,12 +6755,12 @@
       <c r="H119" s="2" t="inlineStr"/>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آواک 🏛️ صنایع ارتباطی آوا 📋 مشخصات کمیته ریسک(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۰:۰۰:۳۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 24 views 06:33 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #غنیلی 🏛️ مجتمع تولیدی نیلی صنعت کرمان 📌 #آگهی_دعوت_به_مجمع_عمومی_عادی_بطور_فوق_العاده 📋 آگهی دعوت به مجمع عمومی عادی بطور فوق العاده 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۵۵:۴۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 06:27 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=k2hoRjExybaGm6oiYoyFNQ%3d%3d&amp;rt=5&amp;let=260&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=JITNjDt8xqdWzPleXQ69FQ%3d%3d&amp;rt=0&amp;let=17&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -6774,7 +6770,7 @@
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247642</t>
+          <t>https://t.me/codalboursetrader/247641</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7761,7 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>ولشرق</t>
+          <t>نیشکر</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -7775,20 +7771,24 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>نیازمند دسته‌بندی دستی</t>
+          <t>گزارش فعالیت ماهانه/تولید و فروش</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr"/>
-      <c r="G139" s="2" t="inlineStr"/>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>گزارش فعالیت ماهانه؛ فعالیت ماهانه</t>
+        </is>
+      </c>
       <c r="H139" s="2" t="inlineStr"/>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ولشرق 🏛️ لیزینگ ایران و شرق 📋 توقف نماد معاملاتی ناشر به استناد ماده ۱۹ مکرر/ ۱۲ مکرر ۳دستورالعمل اجرایی نحوه انجام معاملات 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۵۵:۴۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 23 views 05:27 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #نیشکر 🏛️ توسعه نیشکر و صنایع جانبی ان 📌 #گزارش_فعالیت_ماهانه_دوره_۱_ماهه 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۵۴:۴۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 27 views 05:27 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=n7Ph3S9MMOOObOOOhaiSYkDfGvfw%3d%3d&amp;rt=4&amp;let=140&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=dUgYZ0mlnamZtTOKUsO78A%3d%3d&amp;rt=2&amp;let=8&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247621</t>
+          <t>https://t.me/codalboursetrader/247620</t>
         </is>
       </c>
     </row>
@@ -8345,7 +8345,7 @@
       <c r="H150" s="2" t="inlineStr"/>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تشتاد 🏛️ صنایع تولیدی اشتاد ایران 📌 #آگهی_ثبت_تصمیمات_مجمع_عادی_سالیانه 📋 آگهی ثبت تصمیمات مجمع عمومی عادی بطور فوق العاده دوره ۱۲ ماهه منتهی به ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۷:۴۷:۰۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 33 views 04:18 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تشتاد 🏛️ صنایع تولیدی اشتاد ایران 📌 #آگهی_ثبت_تصمیمات_مجمع_عادی_سالیانه 📋 آگهی ثبت تصمیمات مجمع عمومی عادی بطور فوق العاده دوره ۱۲ ماهه منتهی به ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۷:۴۷:۰۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 34 views 04:18 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
@@ -8399,7 +8399,7 @@
       <c r="H151" s="2" t="inlineStr"/>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #دتولید 🏛️ داروسازی تولید دارو 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۲۰:۴۵:۰۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 56 views 17:15 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #دتولید 🏛️ داروسازی تولید دارو 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۲۰:۴۵:۰۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 57 views 17:15 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
@@ -8453,7 +8453,7 @@
       <c r="H152" s="2" t="inlineStr"/>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #طیور 🏛️ طیور دانه سلامت دزفول 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۳ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی نشده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۴۳:۵۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 59 views 16:15 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #طیور 🏛️ طیور دانه سلامت دزفول 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۳ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی نشده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۴۳:۵۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 60 views 16:15 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
@@ -8507,7 +8507,7 @@
       <c r="H153" s="2" t="inlineStr"/>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سبد_تدبیر 🏛️ سبدگردان تدبیر 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۲۲:۱۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 53 views 15:54 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سبد_تدبیر 🏛️ سبدگردان تدبیر 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۲۲:۱۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 54 views 15:54 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
@@ -8707,7 +8707,7 @@
       <c r="H157" s="2" t="inlineStr"/>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پرسپولیس 🏛️ فرهنگی ورزشی پرسپولیس 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - خرید تیم نونهالان- گروه ب) منتهی به سال مالی ۱۴۰۶/۰۳/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۱۵:۴۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 29 views 15:48 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پرسپولیس 🏛️ فرهنگی ورزشی پرسپولیس 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - خرید تیم نونهالان- گروه ب) منتهی به سال مالی ۱۴۰۶/۰۳/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۱۵:۴۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 30 views 15:48 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
@@ -8757,7 +8757,7 @@
       <c r="H158" s="2" t="inlineStr"/>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #زماهان 🏛️ مجتمع تولید گوشت مرغ ماهان 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (افشای معاملات موضوع ماده ۱۲۹ اصلاحیه قانون تجارت، یا سایر اشخاص وابسته - گروه ب) منتهی به سال مالی ۱۴۰۵/۰۹/۳۰(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۱۱:۳۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 38 views 15:42 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #زماهان 🏛️ مجتمع تولید گوشت مرغ ماهان 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (افشای معاملات موضوع ماده ۱۲۹ اصلاحیه قانون تجارت، یا سایر اشخاص وابسته - گروه ب) منتهی به سال مالی ۱۴۰۵/۰۹/۳۰(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۱۱:۳۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 39 views 15:42 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -8784,22 +8784,22 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>لینک اطلاعیه</t>
+          <t>افشای اطلاعات بااهمیت - (برگزاری مزایده - گروه ب) منتهی به سال مالی ۱۴۰۵/۰۹/۳۰</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>گروه</t>
+          <t>واتی</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:39:04+00:00</t>
+          <t>1405/09/30</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>افشای اطلاعات بااهمیت</t>
+          <t>قرارداد/مناقصه/مزایده</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr"/>
@@ -8807,22 +8807,22 @@
       <c r="H159" s="2" t="inlineStr"/>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تادیکو 🏛️ گروه سرمایه گذاری کشت و دام و صنایع لبنی تامین 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - نتیجه نهایی دعوی له شرکت- گروه ب) منتهی به سال مالی ۱۴۰۶/۰۲/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۰۷:۴۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 38 views 15:39 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #واتی 🏛️ گروه سرمایه گذاری آتیه دماوند 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (برگزاری مزایده - گروه ب) منتهی به سال مالی ۱۴۰۵/۰۹/۳۰ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۳۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 4 views 13:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=cJxlxGJATX7rsNAxKfdNiA%3d%3d&amp;rt=2&amp;let=11&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=7oGwQKFTHYOOObOOO5hgRHJ5cC8A%3d%3d&amp;rt=2&amp;let=11&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>تلگرام بورس‌تریدر</t>
+          <t>بورس‌تریدر؛ تلگرام بورس‌تریدر</t>
         </is>
       </c>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247600</t>
+          <t>https://bourse-trader.ir/index.php?task=codal-reports؛ https://t.me/codalboursetrader/247765</t>
         </is>
       </c>
     </row>
@@ -8836,29 +8836,25 @@
       <c r="C160" s="2" t="inlineStr"/>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>1405/09/30؛ 1405/07/21</t>
+          <t>1405/07/21</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>صورت‌های مالی/حسابرسی</t>
+          <t>نیازمند دسته‌بندی دستی</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr"/>
-      <c r="G160" s="2" t="inlineStr">
-        <is>
-          <t>صورت های مالی؛ صورت‌های مالی</t>
-        </is>
-      </c>
+      <c r="G160" s="2" t="inlineStr"/>
       <c r="H160" s="2" t="inlineStr"/>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>2 واتی گروه سرمایه گذاری آتیه دماوند لینک سابقه معاملات واتی ریز معاملات امروز واتی سهامداران عمده واتی افزایش سرمایه واتی تعدیل قیمت واتی تابلو عرضه و تقاضا صورتهای مالی نسبتهای مالی رتبه بندی بنیادی واتی اندیکاتورها واتی در TSETMC واتی در کدال ن-۲۰ افشای اطلاعات بااهمیت - (برگزاری مزایده - گروه ب) منتهی به سال مالی ۱۴۰۵/۰۹/۳۰ ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۳۸</t>
+          <t>2 پارند ثابت صندوق سرمایه گذاری پارند پایدار سپهر(ETF) تصمیمات مجمع صندوق سرمایه گذاری ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۴۲</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Attachment.aspx?LetterSerial=7oGwQKFTHYOOObOOO5hgRHJ5cC8A%3d%3d</t>
+          <t>https://codal.ir/Reports/Attachment.aspx?LetterSerial=Ng3Xx24F9J07qFLfOOObOOOxOOObOOOXMA%3d%3d</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -8880,39 +8876,35 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>افشای اطلاعات بااهمیت - (برگزاری مزایده - گروه ب) منتهی به سال مالی ۱۴۰۵/۰۹/۳۰</t>
+          <t>صورت وضعیت پورتفوی صندوق سرمایه گذاری دوره ۱ ماهه منتهی به ۱۴۰۵/۰۷/۱۵</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>واتی</t>
+          <t>آسود</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>1405/09/30</t>
+          <t>1405/07/15</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>صورت‌های مالی/حسابرسی</t>
+          <t>نیازمند دسته‌بندی دستی</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr"/>
-      <c r="G161" s="2" t="inlineStr">
-        <is>
-          <t>صورت های مالی؛ صورت‌های مالی</t>
-        </is>
-      </c>
+      <c r="G161" s="2" t="inlineStr"/>
       <c r="H161" s="2" t="inlineStr"/>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>2 واتی گروه سرمایه گذاری آتیه دماوند لینک سابقه معاملات واتی ریز معاملات امروز واتی سهامداران عمده واتی افزایش سرمایه واتی تعدیل قیمت واتی تابلو عرضه و تقاضا صورتهای مالی نسبتهای مالی رتبه بندی بنیادی واتی اندیکاتورها واتی در TSETMC واتی در کدال ن-۲۰ افشای اطلاعات بااهمیت - (برگزاری مزایده - گروه ب) منتهی به سال مالی ۱۴۰۵/۰۹/۳۰</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آسود 🏛️ نهال آرمان اقتصاد 📋 صورت وضعیت پورتفوی صندوق سرمایه گذاری دوره ۱ ماهه منتهی به ۱۴۰۵/۰۷/۱۵ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۳:۵۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 4 views 13:15 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=7oGwQKFTHYOOObOOO5hgRHJ5cC8A%3d%3d&amp;rt=2&amp;let=11&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Attachment.aspx?LetterSerial=7amx5sjE6A0o4pFPOBbvzw%3d%3d</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -8922,7 +8914,7 @@
       </c>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>https://bourse-trader.ir/index.php?task=codal-reports؛ https://t.me/codalboursetrader/247765</t>
+          <t>https://bourse-trader.ir/index.php?task=codal-reports؛ https://t.me/codalboursetrader/247763</t>
         </is>
       </c>
     </row>
@@ -8932,39 +8924,51 @@
           <t>گزارش کدال</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr"/>
-      <c r="C162" s="2" t="inlineStr"/>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) (شرکت توسعه تجارت داتام)</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>وزمین</t>
+        </is>
+      </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>1405/07/21</t>
+          <t>1404/12/29</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>نیازمند دسته‌بندی دستی</t>
+          <t>صورت‌های مالی/حسابرسی</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr"/>
-      <c r="G162" s="2" t="inlineStr"/>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>صورت های مالی؛ صورت‌های مالی</t>
+        </is>
+      </c>
       <c r="H162" s="2" t="inlineStr"/>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>1 پارند ثابت صندوق سرمایه گذاری پارند پایدار سپهر(ETF) تصمیمات مجمع صندوق سرمایه گذاری ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۴۲</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #وزمین 🏛️ بانک ایران زمین 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) (شرکت توسعه تجارت داتام) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۵۴:۴۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 1 view 13:27 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Attachment.aspx?LetterSerial=Ng3Xx24F9J07qFLfOOObOOOxOOObOOOXMA%3d%3d</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=JBsqvslfTvARtL61f2Wg9w%3d%3d&amp;rt=0&amp;let=6&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>بورس‌تریدر</t>
+          <t>بورس‌تریدر؛ تلگرام بورس‌تریدر</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>https://bourse-trader.ir/index.php?task=codal-reports</t>
+          <t>https://bourse-trader.ir/index.php?task=codal-reports؛ https://t.me/codalboursetrader/247767</t>
         </is>
       </c>
     </row>
@@ -8976,31 +8980,19 @@
       </c>
       <c r="B163" s="2" t="inlineStr"/>
       <c r="C163" s="2" t="inlineStr"/>
-      <c r="D163" s="2" t="inlineStr">
-        <is>
-          <t>1405/07/21</t>
-        </is>
-      </c>
+      <c r="D163" s="2" t="inlineStr"/>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>صورت‌های مالی/حسابرسی</t>
+          <t>نیازمند دسته‌بندی دستی</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr"/>
-      <c r="G163" s="2" t="inlineStr">
-        <is>
-          <t>صورت های مالی؛ صورت‌های مالی</t>
-        </is>
-      </c>
+      <c r="G163" s="2" t="inlineStr"/>
       <c r="H163" s="2" t="inlineStr"/>
-      <c r="I163" s="2" t="inlineStr">
-        <is>
-          <t>5 ولملت واسپاری ملت لینک سابقه معاملات ولملت ریز معاملات امروز ولملت سهامداران عمده ولملت افزایش سرمایه ولملت تعدیل قیمت ولملت تابلو عرضه و تقاضا صورتهای مالی نسبتهای مالی رتبه بندی بنیادی ولملت اندیکاتورها ولملت در TSETMC ولملت در کدال توقف نماد معاملاتی ناشر به استناد ماده ۱۹ مکرر/ ۱۲ مکرر ۳دستورالعمل اجرایی نحوه انجام معاملات ۱۴۰۵/۰۷/۲۱ ۱۶:۴۲:۳۰</t>
-        </is>
-      </c>
+      <c r="I163" s="2" t="inlineStr"/>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Attachment.aspx?LetterSerial=K262scVeIjiNRrMfOOObOOOgvquQ%3d%3d</t>
+          <t>https://codal.ir/Reports/Attachment.aspx?LetterSerial=JBsqvslfTvARtL61f2Wg9w%3d%3d</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -9022,31 +9014,19 @@
       </c>
       <c r="B164" s="2" t="inlineStr"/>
       <c r="C164" s="2" t="inlineStr"/>
-      <c r="D164" s="2" t="inlineStr">
-        <is>
-          <t>1405/07/21</t>
-        </is>
-      </c>
+      <c r="D164" s="2" t="inlineStr"/>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>صورت‌های مالی/حسابرسی</t>
+          <t>نیازمند دسته‌بندی دستی</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr"/>
-      <c r="G164" s="2" t="inlineStr">
-        <is>
-          <t>صورت های مالی؛ صورت‌های مالی</t>
-        </is>
-      </c>
+      <c r="G164" s="2" t="inlineStr"/>
       <c r="H164" s="2" t="inlineStr"/>
-      <c r="I164" s="2" t="inlineStr">
-        <is>
-          <t>3 پاسا ایران یاسا تایر و رابر لینک سابقه معاملات پاسا ریز معاملات امروز پاسا سهامداران عمده پاسا افزایش سرمایه پاسا تعدیل قیمت پاسا تابلو عرضه و تقاضا صورتهای مالی نسبتهای مالی رتبه بندی بنیادی پاسا اندیکاتورها پاسا در TSETMC پاسا در کدال مشخصات کمیته ریسک ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۳۲</t>
-        </is>
-      </c>
+      <c r="I164" s="2" t="inlineStr"/>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Attachment.aspx?LetterSerial=1VmkDbw3qGy6TeKjT0burw%3d%3d</t>
+          <t>https://codal.ir/Reports/Attachment.aspx?LetterSerial=7oGwQKFTHYOOObOOO5hgRHJ5cC8A%3d%3d</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -9066,51 +9046,31 @@
           <t>گزارش کدال</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>صورت وضعیت پورتفوی صندوق سرمایه گذاری دوره ۱ ماهه منتهی به ۱۴۰۵/۰۷/۱۵</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>آسود</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
-        <is>
-          <t>1405/07/15</t>
-        </is>
-      </c>
+      <c r="B165" s="2" t="inlineStr"/>
+      <c r="C165" s="2" t="inlineStr"/>
+      <c r="D165" s="2" t="inlineStr"/>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>صورت‌های مالی/حسابرسی</t>
+          <t>نیازمند دسته‌بندی دستی</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr"/>
-      <c r="G165" s="2" t="inlineStr">
-        <is>
-          <t>صورت های مالی؛ صورت‌های مالی</t>
-        </is>
-      </c>
+      <c r="G165" s="2" t="inlineStr"/>
       <c r="H165" s="2" t="inlineStr"/>
-      <c r="I165" s="2" t="inlineStr">
-        <is>
-          <t>4 آسود نهال آرمان اقتصاد لینک سابقه معاملات آسود ریز معاملات امروز آسود سهامداران عمده آسود افزایش سرمایه آسود تعدیل قیمت آسود تابلو عرضه و تقاضا صورتهای مالی نسبتهای مالی رتبه بندی بنیادی آسود اندیکاتورها آسود در TSETMC آسود در کدال صورت وضعیت پورتفوی صندوق سرمایه گذاری دوره ۱ ماهه منتهی به ۱۴۰۵/۰۷/۱۵ ۱۴۰۵/۰۷/۲۱ ۱۶:۴۳:۵۷</t>
-        </is>
-      </c>
+      <c r="I165" s="2" t="inlineStr"/>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Attachment.aspx?LetterSerial=7amx5sjE6A0o4pFPOBbvzw%3d%3d</t>
+          <t>https://codal.ir/Reports/Attachment.aspx?LetterSerial=1VmkDbw3qGy6TeKjT0burw%3d%3d</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>بورس‌تریدر؛ تلگرام بورس‌تریدر</t>
+          <t>بورس‌تریدر</t>
         </is>
       </c>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>https://bourse-trader.ir/index.php?task=codal-reports؛ https://t.me/codalboursetrader/247763</t>
+          <t>https://bourse-trader.ir/index.php?task=codal-reports</t>
         </is>
       </c>
     </row>
@@ -9126,7 +9086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9276,12 +9236,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>تبرک</t>
+          <t>غبهار</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:42:06+00:00</t>
+          <t>2026-10-13T10:06:04+00:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -9298,12 +9258,12 @@
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تبرک 🏛️ گروه کارخانجات صنعتی تبرک 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - اجازه بهره برداری- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۰۹:۵۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 21 views 10:42 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #غبهار 🏛️ کشت و صنعت بهاران گلبهار خراسان 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - اجازه بهره برداری از برند- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۳۴:۲۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 24 views 10:06 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=5XQQQaQQQKiXjQjKpTJ7Ei9Op6HA%3d%3d&amp;rt=2&amp;let=11&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=cQQQaQQQVSzY5r93cLOOObOOOHVaEpC5Rw%3d%3d&amp;rt=0&amp;let=11&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -9313,66 +9273,12 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247705</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>گزارش کدال</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>لینک اطلاعیه</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>غبهار</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13T10:06:04+00:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>طرح توسعه/پروژه</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>بهره برداری؛ بهره‌برداری</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #غبهار 🏛️ کشت و صنعت بهاران گلبهار خراسان 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - اجازه بهره برداری از برند- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۳۴:۲۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 24 views 10:06 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=cQQQaQQQVSzY5r93cLOOObOOOHVaEpC5Rw%3d%3d&amp;rt=0&amp;let=11&amp;ct=0&amp;ft=-1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>تلگرام بورس‌تریدر</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
           <t>https://t.me/codalboursetrader/247691</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L4"/>
+  <autoFilter ref="A1:L3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9383,7 +9289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9470,17 +9376,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>مشخصات کمیته ریسک</t>
+          <t>لینک اطلاعیه</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>پاسا</t>
+          <t>افران</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T13:18:08+00:00</t>
+          <t>2026-10-13T13:12:07+00:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -9497,22 +9403,22 @@
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>3 پاسا ایران یاسا تایر و رابر لینک سابقه معاملات پاسا ریز معاملات امروز پاسا سهامداران عمده پاسا افزایش سرمایه پاسا تعدیل قیمت پاسا تابلو عرضه و تقاضا صورتهای مالی نسبتهای مالی رتبه بندی بنیادی پاسا اندیکاتورها پاسا در TSETMC پاسا در کدال مشخصات کمیته ریسک</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #افران 🏛️ افرا نماد پایدار 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۵/۰۵/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۱:۲۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 6 views 13:12 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=1VmkDbw3qGy6TeKjT0burw%3d%3d&amp;rt=0&amp;let=260&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=r2RrHefXhTNZFw8HmjCTZQ%3d%3d&amp;rt=2&amp;let=6&amp;ct=5&amp;ft=4</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>بورس‌تریدر؛ تلگرام بورس‌تریدر</t>
+          <t>تلگرام بورس‌تریدر</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>https://bourse-trader.ir/index.php?task=codal-reports؛ https://t.me/codalboursetrader/247764</t>
+          <t>https://t.me/codalboursetrader/247760</t>
         </is>
       </c>
     </row>
@@ -9524,17 +9430,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>توقف نماد معاملاتی ناشر به استناد ماده ۱۹ مکرر/ ۱۲ مکرر ۳دستورالعمل اجرایی نحوه انجام معاملات</t>
+          <t>لینک اطلاعیه</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>ولملت</t>
+          <t>ستران</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T13:15:06+00:00</t>
+          <t>2026-10-13T13:06:05+00:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -9551,22 +9457,22 @@
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>5 ولملت واسپاری ملت لینک سابقه معاملات ولملت ریز معاملات امروز ولملت سهامداران عمده ولملت افزایش سرمایه ولملت تعدیل قیمت ولملت تابلو عرضه و تقاضا صورتهای مالی نسبتهای مالی رتبه بندی بنیادی ولملت اندیکاتورها ولملت در TSETMC ولملت در کدال توقف نماد معاملاتی ناشر به استناد ماده ۱۹ مکرر/ ۱۲ مکرر ۳دستورالعمل اجرایی نحوه انجام معاملات</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ستران 🏛️ سیمان تهران 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۴/۳۱ (حسابرسی شده) (شرکت صنایع سیمان گیلان سبز) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۳۴:۵۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 9 views 13:06 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=K262scVeIjiNRrMfOOObOOOgvquQ%3d%3d&amp;rt=4&amp;let=140&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=J1aPpo73eSoo2Dong5HGyg%3d%3d&amp;rt=0&amp;let=6&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>بورس‌تریدر؛ تلگرام بورس‌تریدر</t>
+          <t>تلگرام بورس‌تریدر</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>https://bourse-trader.ir/index.php?task=codal-reports؛ https://t.me/codalboursetrader/247762</t>
+          <t>https://t.me/codalboursetrader/247757</t>
         </is>
       </c>
     </row>
@@ -9583,12 +9489,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>افران</t>
+          <t>پیمان</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T13:12:07+00:00</t>
+          <t>2026-10-13T12:57:04+00:00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9605,12 +9511,12 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #افران 🏛️ افرا نماد پایدار 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۵/۰۵/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۱:۲۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 6 views 13:12 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 توضیحات در خصوص اطلاعات و صورت های مالی منتشر شده 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۲۴:۴۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 11 views 12:57 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=r2RrHefXhTNZFw8HmjCTZQ%3d%3d&amp;rt=2&amp;let=6&amp;ct=5&amp;ft=4</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=8dkDNPgxRGjPL9ot5QQQaQQQ6m9Q%3d%3d&amp;rt=5&amp;let=174&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -9620,7 +9526,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247760</t>
+          <t>https://t.me/codalboursetrader/247752</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9543,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>ستران</t>
+          <t>ثنا</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T13:06:05+00:00</t>
+          <t>2026-10-13T12:15:05+00:00</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -9659,12 +9565,12 @@
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ستران 🏛️ سیمان تهران 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۴/۳۱ (حسابرسی شده) (شرکت صنایع سیمان گیلان سبز) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۳۴:۵۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 9 views 13:06 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ثنا 🏛️ زرین نهال ثنا 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۴۲:۰۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 12:15 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=J1aPpo73eSoo2Dong5HGyg%3d%3d&amp;rt=0&amp;let=6&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=p3YYElxIlOXNpKcxvKb4kw%3d%3d&amp;rt=2&amp;let=6&amp;ct=5&amp;ft=4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -9674,7 +9580,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247757</t>
+          <t>https://t.me/codalboursetrader/247738</t>
         </is>
       </c>
     </row>
@@ -9691,12 +9597,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>پیمان</t>
+          <t>آلا</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:57:04+00:00</t>
+          <t>2026-10-13T12:12:07+00:00</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -9713,12 +9619,12 @@
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 توضیحات در خصوص اطلاعات و صورت های مالی منتشر شده 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۲۴:۴۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 11 views 12:57 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آلا 🏛️ اعتماد ارغوان 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۴۱:۳۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 12:12 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=8dkDNPgxRGjPL9ot5QQQaQQQ6m9Q%3d%3d&amp;rt=5&amp;let=174&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=cr2KkEseV1SvOu3ZCycmug%3d%3d&amp;rt=2&amp;let=6&amp;ct=5&amp;ft=2</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -9728,7 +9634,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247752</t>
+          <t>https://t.me/codalboursetrader/247736</t>
         </is>
       </c>
     </row>
@@ -9745,12 +9651,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ثنا</t>
+          <t>واعتماد</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:15:05+00:00</t>
+          <t>2026-10-13T11:54:04+00:00</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -9767,12 +9673,12 @@
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ثنا 🏛️ زرین نهال ثنا 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۴۲:۰۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 16 views 12:15 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #واعتماد 🏛️ سرمایه گذاری توسعه اعتماد 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ (حسابرسی نشده)(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۲۲:۳۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 9 views 11:54 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=p3YYElxIlOXNpKcxvKb4kw%3d%3d&amp;rt=2&amp;let=6&amp;ct=5&amp;ft=4</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=AhmPLM0rSuvgMOOObOOOkQQQaQQQKkQJrQ%3d%3d&amp;rt=2&amp;let=6&amp;ct=2&amp;ft=-1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -9782,7 +9688,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247738</t>
+          <t>https://t.me/codalboursetrader/247731</t>
         </is>
       </c>
     </row>
@@ -9799,12 +9705,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>آلا</t>
+          <t>کی ام سی</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:12:07+00:00</t>
+          <t>2026-10-13T11:30:09+00:00</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -9815,18 +9721,18 @@
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>صورت های مالی؛ صورت‌های مالی</t>
+          <t>صورت های مالی؛ صورت‌های مالی؛ گزارش فعالیت ماهانه؛ فعالیت ماهانه</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آلا 🏛️ اعتماد ارغوان 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۴۱:۳۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 12:12 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کی_ام_سی 🏛️ کرمان موتور 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۴/۰۷/۳۰ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۵۹:۳۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 14 views 11:30 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=cr2KkEseV1SvOu3ZCycmug%3d%3d&amp;rt=2&amp;let=6&amp;ct=5&amp;ft=2</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=aoCafEWSkkL36C63gVbsWQ%3d%3d&amp;rt=0&amp;let=58&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -9836,7 +9742,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247736</t>
+          <t>https://t.me/codalboursetrader/247725</t>
         </is>
       </c>
     </row>
@@ -9853,12 +9759,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>واعتماد</t>
+          <t>پناه</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:54:04+00:00</t>
+          <t>2026-10-13T11:24:03+00:00</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -9875,12 +9781,12 @@
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #واعتماد 🏛️ سرمایه گذاری توسعه اعتماد 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ (حسابرسی نشده)(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۲۲:۳۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 8 views 11:54 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پناه 🏛️ بخشی شایسته فردا 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۵/۰۵/۱۵ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۵۲:۱۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 11:24 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=AhmPLM0rSuvgMOOObOOOkQQQaQQQKkQJrQ%3d%3d&amp;rt=2&amp;let=6&amp;ct=2&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=NGXNR8aVLmylLhNsEd8rVw%3d%3d&amp;rt=2&amp;let=6&amp;ct=5&amp;ft=4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -9890,7 +9796,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247731</t>
+          <t>https://t.me/codalboursetrader/247720</t>
         </is>
       </c>
     </row>
@@ -9907,12 +9813,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>پناه</t>
+          <t>آتیه</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:24:03+00:00</t>
+          <t>2026-10-13T11:12:07+00:00</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -9929,12 +9835,12 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پناه 🏛️ بخشی شایسته فردا 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۵/۰۵/۱۵ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۵۲:۱۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 11:24 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آتیه 🏛️ تامین آتیه کارکنان صنعت برق خراسان 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) (شرکت خدمات بیمه ای آتیه صنعت برق شمس) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۴۰:۰۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 11:12 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=NGXNR8aVLmylLhNsEd8rVw%3d%3d&amp;rt=2&amp;let=6&amp;ct=5&amp;ft=4</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=p9QQQaQQQQsIbmyCQQQaQQQjbUckCy26rw%3d%3d&amp;rt=5&amp;let=6&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -9944,7 +9850,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247720</t>
+          <t>https://t.me/codalboursetrader/247716</t>
         </is>
       </c>
     </row>
@@ -9966,7 +9872,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:12:07+00:00</t>
+          <t>2026-10-13T11:12:05+00:00</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -9983,12 +9889,12 @@
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آتیه 🏛️ تامین آتیه کارکنان صنعت برق خراسان 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) (شرکت خدمات بیمه ای آتیه صنعت برق شمس) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۴۰:۰۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 11:12 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آتیه 🏛️ تامین آتیه کارکنان صنعت برق خراسان 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) (شرکت کارگزاری رسمی بیمه آتیه گستر آرامش سناباد) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۳۹:۰۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 15 views 11:12 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=p9QQQaQQQQsIbmyCQQQaQQQjbUckCy26rw%3d%3d&amp;rt=5&amp;let=6&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=3cPc8MGy81Y6AOOObOOOBim61l2A%3d%3d&amp;rt=5&amp;let=6&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -9998,7 +9904,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247716</t>
+          <t>https://t.me/codalboursetrader/247715</t>
         </is>
       </c>
     </row>
@@ -10020,7 +9926,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:12:05+00:00</t>
+          <t>2026-10-13T11:09:05+00:00</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -10028,7 +9934,11 @@
           <t>صورت‌های مالی/حسابرسی</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>راه اندازی؛ راه‌اندازی</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>صورت های مالی؛ صورت‌های مالی</t>
@@ -10037,12 +9947,12 @@
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آتیه 🏛️ تامین آتیه کارکنان صنعت برق خراسان 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) (شرکت کارگزاری رسمی بیمه آتیه گستر آرامش سناباد) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۳۹:۰۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 15 views 11:12 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آتیه 🏛️ تامین آتیه کارکنان صنعت برق خراسان 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) (شرکت احداث وراه اندازی تاسیسات انرژی اتیه سناباد آرتا) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۳۷:۳۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 11:09 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=3cPc8MGy81Y6AOOObOOOBim61l2A%3d%3d&amp;rt=5&amp;let=6&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=UvIWOOObOOO0tMGKySDxDoDQQQaQQQJKTw%3d%3d&amp;rt=5&amp;let=6&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -10052,7 +9962,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247715</t>
+          <t>https://t.me/codalboursetrader/247714</t>
         </is>
       </c>
     </row>
@@ -10069,12 +9979,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>آتیه</t>
+          <t>تلاشگستران آینده</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:09:05+00:00</t>
+          <t>2026-10-13T10:57:04+00:00</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -10082,11 +9992,7 @@
           <t>صورت‌های مالی/حسابرسی</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>راه اندازی؛ راه‌اندازی</t>
-        </is>
-      </c>
+      <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
           <t>صورت های مالی؛ صورت‌های مالی</t>
@@ -10095,12 +10001,12 @@
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آتیه 🏛️ تامین آتیه کارکنان صنعت برق خراسان 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) (شرکت احداث وراه اندازی تاسیسات انرژی اتیه سناباد آرتا) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۳۷:۳۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 11:09 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تلاشگستران_آینده 🏛️ تلاش گستران آینده 📌 #صورت_های_مالی_میان_دوره_ای 📋 مشمول اصل ۴۴ - صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۲۵:۴۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 19 views 10:57 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=UvIWOOObOOO0tMGKySDxDoDQQQaQQQJKTw%3d%3d&amp;rt=5&amp;let=6&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=sY2QQQaQQQyZjTd77yEfU0Zfo64A%3d%3d&amp;rt=2&amp;let=6&amp;ct=13&amp;ft=-1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -10110,7 +10016,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247714</t>
+          <t>https://t.me/codalboursetrader/247710</t>
         </is>
       </c>
     </row>
@@ -10127,12 +10033,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>تلاشگستران آینده</t>
+          <t>وپاسار</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:57:04+00:00</t>
+          <t>2026-10-13T10:45:07+00:00</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -10149,12 +10055,12 @@
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تلاشگستران_آینده 🏛️ تلاش گستران آینده 📌 #صورت_های_مالی_میان_دوره_ای 📋 مشمول اصل ۴۴ - صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۲۵:۴۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 19 views 10:57 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #وپاسار 🏛️ بانک پاسارگاد 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) (شرکت مدیریت ساختمانی آریان پاسارگاد) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۱۳:۱۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 25 views 10:45 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=sY2QQQaQQQyZjTd77yEfU0Zfo64A%3d%3d&amp;rt=2&amp;let=6&amp;ct=13&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=MnQQQaQQQqAa9B8Hcrzvj1xCh2KA%3d%3d&amp;rt=1&amp;let=6&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -10164,7 +10070,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247710</t>
+          <t>https://t.me/codalboursetrader/247707</t>
         </is>
       </c>
     </row>
@@ -10181,12 +10087,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>وپاسار</t>
+          <t>بمولد</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:45:07+00:00</t>
+          <t>2026-10-13T10:36:08+00:00</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -10197,18 +10103,18 @@
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>صورت های مالی؛ صورت‌های مالی</t>
+          <t>صورت های مالی؛ صورت‌های مالی؛ گزارش فعالیت ماهانه؛ فعالیت ماهانه</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #وپاسار 🏛️ بانک پاسارگاد 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) (شرکت مدیریت ساختمانی آریان پاسارگاد) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۱۳:۱۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 25 views 10:45 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #بمولد 🏛️ مولد نیروگاهی تجارت فارس 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۰۴:۰۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 10:36 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=MnQQQaQQQqAa9B8Hcrzvj1xCh2KA%3d%3d&amp;rt=1&amp;let=6&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=Xl0KnYaKngPe74XyHCp6QA%3d%3d&amp;rt=0&amp;let=58&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -10218,7 +10124,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247707</t>
+          <t>https://t.me/codalboursetrader/247702</t>
         </is>
       </c>
     </row>
@@ -10235,34 +10141,34 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>بمولد</t>
+          <t>و پایدار</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:36:08+00:00</t>
+          <t>2026-10-13T10:27:04+00:00</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>صورت‌های مالی/حسابرسی</t>
+          <t>گزارش فعالیت ماهانه/تولید و فروش</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>صورت های مالی؛ صورت‌های مالی؛ گزارش فعالیت ماهانه؛ فعالیت ماهانه</t>
+          <t>گزارش فعالیت ماهانه؛ فعالیت ماهانه</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #بمولد 🏛️ مولد نیروگاهی تجارت فارس 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۰۴:۰۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 10:36 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #و_پایدار 🏛️ سرمایه گذاری توسعه اقتصاد پایدار سینا 📌 #گزارش_فعالیت_ماهانه_دوره_۱_ماهه 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۵۴:۳۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 10:27 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=Xl0KnYaKngPe74XyHCp6QA%3d%3d&amp;rt=0&amp;let=58&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=d1sKjOOObOOOj3jgDeLsweyuKCqA%3d%3d&amp;rt=2&amp;let=8&amp;ct=2&amp;ft=-1</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -10272,7 +10178,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247702</t>
+          <t>https://t.me/codalboursetrader/247697</t>
         </is>
       </c>
     </row>
@@ -10289,34 +10195,34 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>و پایدار</t>
+          <t>هانیکو</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:27:04+00:00</t>
+          <t>2026-10-13T10:00:06+00:00</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>گزارش فعالیت ماهانه/تولید و فروش</t>
+          <t>صورت‌های مالی/حسابرسی</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>گزارش فعالیت ماهانه؛ فعالیت ماهانه</t>
+          <t>صورت های مالی؛ صورت‌های مالی؛ گزارش فعالیت ماهانه؛ فعالیت ماهانه</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #و_پایدار 🏛️ سرمایه گذاری توسعه اقتصاد پایدار سینا 📌 #گزارش_فعالیت_ماهانه_دوره_۱_ماهه 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۵۴:۳۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 10:27 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #هانیکو 🏛️ هامون نایزه 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۲۷:۱۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 27 views 10:00 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=d1sKjOOObOOOj3jgDeLsweyuKCqA%3d%3d&amp;rt=2&amp;let=8&amp;ct=2&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=vjOOObOOONlQQQaQQQRUVIcoPjm3kOOObOOOvE7Q%3d%3d&amp;rt=0&amp;let=58&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -10326,7 +10232,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247697</t>
+          <t>https://t.me/codalboursetrader/247690</t>
         </is>
       </c>
     </row>
@@ -10343,12 +10249,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>هانیکو</t>
+          <t>پیمان</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:00:06+00:00</t>
+          <t>2026-10-13T09:57:04+00:00</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -10365,12 +10271,12 @@
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #هانیکو 🏛️ هامون نایزه 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۲۷:۱۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 27 views 10:00 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۴/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۲۵:۲۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 25 views 09:57 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=vjOOObOOONlQQQaQQQRUVIcoPjm3kOOObOOOvE7Q%3d%3d&amp;rt=0&amp;let=58&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=6QQQaQQQagOFzsInZzrvSeYgoQKw%3d%3d&amp;rt=5&amp;let=58&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -10380,7 +10286,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247690</t>
+          <t>https://t.me/codalboursetrader/247689</t>
         </is>
       </c>
     </row>
@@ -10402,7 +10308,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T09:57:04+00:00</t>
+          <t>2026-10-13T09:54:07+00:00</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -10419,12 +10325,12 @@
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۴/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۲۵:۲۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 25 views 09:57 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۵/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۲۲:۳۶ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 09:54 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=6QQQaQQQagOFzsInZzrvSeYgoQKw%3d%3d&amp;rt=5&amp;let=58&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=0mlSbVGyRTHDS5FCa37pRQ%3d%3d&amp;rt=5&amp;let=58&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -10434,7 +10340,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247689</t>
+          <t>https://t.me/codalboursetrader/247688</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10362,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T09:54:07+00:00</t>
+          <t>2026-10-13T09:48:11+00:00</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -10473,12 +10379,12 @@
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۵/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۲۲:۳۶ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 09:54 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۱۷:۲۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 09:48 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=0mlSbVGyRTHDS5FCa37pRQ%3d%3d&amp;rt=5&amp;let=58&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=OOObOOOmOJQNA1YFIqLQMBuVjtzg%3d%3d&amp;rt=5&amp;let=58&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -10488,7 +10394,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247688</t>
+          <t>https://t.me/codalboursetrader/247687</t>
         </is>
       </c>
     </row>
@@ -10505,12 +10411,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>پیمان</t>
+          <t>ذوب</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T09:48:11+00:00</t>
+          <t>2026-10-13T09:15:04+00:00</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -10521,18 +10427,18 @@
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>صورت های مالی؛ صورت‌های مالی؛ گزارش فعالیت ماهانه؛ فعالیت ماهانه</t>
+          <t>صورت های مالی؛ صورت‌های مالی</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۱۷:۲۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 09:48 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ذوب 🏛️ ذوب آهن اصفهان 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) (شرکت باشگاه فرهنگی ورزشی ذوب آهن اصفهان) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۴۳:۰۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 26 views 09:15 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=OOObOOOmOJQNA1YFIqLQMBuVjtzg%3d%3d&amp;rt=5&amp;let=58&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=fgXQQQaQQQOgUxIgsByNA8mRk5Ng%3d%3d&amp;rt=5&amp;let=6&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -10542,7 +10448,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247687</t>
+          <t>https://t.me/codalboursetrader/247677</t>
         </is>
       </c>
     </row>
@@ -10559,34 +10465,34 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>ذوب</t>
+          <t>هلد سینا</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T09:15:04+00:00</t>
+          <t>2026-10-13T08:57:05+00:00</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>صورت‌های مالی/حسابرسی</t>
+          <t>گزارش فعالیت ماهانه/تولید و فروش</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>صورت های مالی؛ صورت‌های مالی</t>
+          <t>گزارش فعالیت ماهانه؛ فعالیت ماهانه</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ذوب 🏛️ ذوب آهن اصفهان 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) (شرکت باشگاه فرهنگی ورزشی ذوب آهن اصفهان) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۴۳:۰۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 26 views 09:15 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #هلد_سینا 🏛️ مادر تخصصی مالی و سرمایه گذاری سینا 📌 #گزارش_فعالیت_ماهانه_دوره_۱_ماهه 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۲۴:۴۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 08:57 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=fgXQQQaQQQOgUxIgsByNA8mRk5Ng%3d%3d&amp;rt=5&amp;let=6&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=OIDCIRuyfakSdfQQQaQQQXWptIbA%3d%3d&amp;rt=2&amp;let=8&amp;ct=2&amp;ft=-1</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -10596,7 +10502,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247677</t>
+          <t>https://t.me/codalboursetrader/247672</t>
         </is>
       </c>
     </row>
@@ -10613,34 +10519,34 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>هلد سینا</t>
+          <t>سبد ایرانیان</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T08:57:05+00:00</t>
+          <t>2026-10-13T08:21:18+00:00</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>گزارش فعالیت ماهانه/تولید و فروش</t>
+          <t>صورت‌های مالی/حسابرسی</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>گزارش فعالیت ماهانه؛ فعالیت ماهانه</t>
+          <t>صورت های مالی؛ صورت‌های مالی</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #هلد_سینا 🏛️ مادر تخصصی مالی و سرمایه گذاری سینا 📌 #گزارش_فعالیت_ماهانه_دوره_۱_ماهه 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۲۴:۴۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 08:57 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سبد_ایرانیان 🏛️ سبد گردان سرمایه ایرانیان 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ (حسابرسی نشده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۴۹:۵۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 15 views 08:21 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=OIDCIRuyfakSdfQQQaQQQXWptIbA%3d%3d&amp;rt=2&amp;let=8&amp;ct=2&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=3SSguRuUSSavWb2H3lIgOOObOOOw%3d%3d&amp;rt=2&amp;let=6&amp;ct=6&amp;ft=-1</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -10650,7 +10556,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247672</t>
+          <t>https://t.me/codalboursetrader/247667</t>
         </is>
       </c>
     </row>
@@ -10667,12 +10573,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>سبد ایرانیان</t>
+          <t>کسعدی</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T08:21:18+00:00</t>
+          <t>2026-10-13T08:00:13+00:00</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -10683,18 +10589,18 @@
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>صورت های مالی؛ صورت‌های مالی</t>
+          <t>صورت های مالی؛ صورت‌های مالی؛ گزارش فعالیت ماهانه؛ فعالیت ماهانه</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سبد_ایرانیان 🏛️ سبد گردان سرمایه ایرانیان 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ (حسابرسی نشده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۴۹:۵۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 15 views 08:21 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کسعدی 🏛️ کارخانجات کاشی و سرامیک سعدی 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۲۷:۴۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 16 views 08:00 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=3SSguRuUSSavWb2H3lIgOOObOOOw%3d%3d&amp;rt=2&amp;let=6&amp;ct=6&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=163NzE0XtsLfeG4Va20D3A%3d%3d&amp;rt=0&amp;let=58&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -10704,7 +10610,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247667</t>
+          <t>https://t.me/codalboursetrader/247662</t>
         </is>
       </c>
     </row>
@@ -11153,34 +11059,34 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>مروارید</t>
+          <t>نیشکر</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T04:42:06+00:00</t>
+          <t>2026-10-13T05:27:06+00:00</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>صورت‌های مالی/حسابرسی</t>
+          <t>گزارش فعالیت ماهانه/تولید و فروش</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>صورت های مالی؛ صورت‌های مالی</t>
+          <t>گزارش فعالیت ماهانه؛ فعالیت ماهانه</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #مروارید 🏛️ مروارید آتا 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۳ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ (حسابرسی نشده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۰۹:۰۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 04:42 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #نیشکر 🏛️ توسعه نیشکر و صنایع جانبی ان 📌 #گزارش_فعالیت_ماهانه_دوره_۱_ماهه 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۵۴:۴۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 27 views 05:27 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=S34cvdapSqlS1v8qORMa0A%3d%3d&amp;rt=2&amp;let=6&amp;ct=5&amp;ft=4</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=dUgYZ0mlnamZtTOKUsO78A%3d%3d&amp;rt=2&amp;let=8&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -11190,7 +11096,7 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247612</t>
+          <t>https://t.me/codalboursetrader/247620</t>
         </is>
       </c>
     </row>
@@ -11207,12 +11113,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>فن آوا</t>
+          <t>مروارید</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T04:39:06+00:00</t>
+          <t>2026-10-13T04:42:06+00:00</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -11229,12 +11135,12 @@
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #فن_آوا 🏛️ گروه فن اوا 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) (شرکت تضمین گستر فن آوا) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۰۶:۴۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 26 views 04:39 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #مروارید 🏛️ مروارید آتا 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۳ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ (حسابرسی نشده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۰۹:۰۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 04:42 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=dHOOObOOOl8VEieAmP0XiDmUv6Sw%3d%3d&amp;rt=5&amp;let=6&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=S34cvdapSqlS1v8qORMa0A%3d%3d&amp;rt=2&amp;let=6&amp;ct=5&amp;ft=4</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -11244,7 +11150,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247611</t>
+          <t>https://t.me/codalboursetrader/247612</t>
         </is>
       </c>
     </row>
@@ -11261,12 +11167,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>درین</t>
+          <t>فن آوا</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T04:27:05+00:00</t>
+          <t>2026-10-13T04:39:06+00:00</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -11283,12 +11189,12 @@
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #درین 🏛️ درین آتا 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۳ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ (حسابرسی نشده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۷:۵۴:۱۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 32 views 04:27 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #فن_آوا 🏛️ گروه فن اوا 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) (شرکت تضمین گستر فن آوا) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۰۶:۴۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 26 views 04:39 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=ryk6bG0NDzYmxxuxO9bvBA%3d%3d&amp;rt=2&amp;let=6&amp;ct=5&amp;ft=2</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=dHOOObOOOl8VEieAmP0XiDmUv6Sw%3d%3d&amp;rt=5&amp;let=6&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -11298,7 +11204,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247610</t>
+          <t>https://t.me/codalboursetrader/247611</t>
         </is>
       </c>
     </row>
@@ -11315,12 +11221,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>دتولید</t>
+          <t>درین</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T17:15:14+00:00</t>
+          <t>2026-10-13T04:27:05+00:00</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -11337,12 +11243,12 @@
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #دتولید 🏛️ داروسازی تولید دارو 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۲۰:۴۵:۰۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 56 views 17:15 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #درین 🏛️ درین آتا 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۳ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ (حسابرسی نشده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۷:۵۴:۱۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 32 views 04:27 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=l21PuUrWBCHsiu3B7MxwPg%3d%3d&amp;rt=0&amp;let=6&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=ryk6bG0NDzYmxxuxO9bvBA%3d%3d&amp;rt=2&amp;let=6&amp;ct=5&amp;ft=2</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -11352,7 +11258,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247608</t>
+          <t>https://t.me/codalboursetrader/247610</t>
         </is>
       </c>
     </row>
@@ -11369,12 +11275,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>طیور</t>
+          <t>دتولید</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T16:15:17+00:00</t>
+          <t>2026-10-12T17:15:14+00:00</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -11391,12 +11297,12 @@
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #طیور 🏛️ طیور دانه سلامت دزفول 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۳ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی نشده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۴۳:۵۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 59 views 16:15 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #دتولید 🏛️ داروسازی تولید دارو 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۲۰:۴۵:۰۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 57 views 17:15 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=7u3CiNfKYKJo8clsvovoXg%3d%3d&amp;rt=0&amp;let=6&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=l21PuUrWBCHsiu3B7MxwPg%3d%3d&amp;rt=0&amp;let=6&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -11406,7 +11312,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247607</t>
+          <t>https://t.me/codalboursetrader/247608</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11329,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>سبد تدبیر</t>
+          <t>طیور</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:54:06+00:00</t>
+          <t>2026-10-12T16:15:17+00:00</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -11445,12 +11351,12 @@
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سبد_تدبیر 🏛️ سبدگردان تدبیر 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۲۲:۱۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 53 views 15:54 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #طیور 🏛️ طیور دانه سلامت دزفول 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۳ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی نشده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۴۳:۵۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 60 views 16:15 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=CemFgWQQQaQQQtAtAoiBU77x1BZg%3d%3d&amp;rt=2&amp;let=6&amp;ct=6&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=7u3CiNfKYKJo8clsvovoXg%3d%3d&amp;rt=0&amp;let=6&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -11460,7 +11366,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247606</t>
+          <t>https://t.me/codalboursetrader/247607</t>
         </is>
       </c>
     </row>
@@ -11470,11 +11376,19 @@
           <t>گزارش کدال</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr"/>
-      <c r="C39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>لینک اطلاعیه</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>سبد تدبیر</t>
+        </is>
+      </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1405/09/30؛ 1405/07/21</t>
+          <t>2026-10-12T15:54:06+00:00</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -11491,22 +11405,22 @@
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2 واتی گروه سرمایه گذاری آتیه دماوند لینک سابقه معاملات واتی ریز معاملات امروز واتی سهامداران عمده واتی افزایش سرمایه واتی تعدیل قیمت واتی تابلو عرضه و تقاضا صورتهای مالی نسبتهای مالی رتبه بندی بنیادی واتی اندیکاتورها واتی در TSETMC واتی در کدال ن-۲۰ افشای اطلاعات بااهمیت - (برگزاری مزایده - گروه ب) منتهی به سال مالی ۱۴۰۵/۰۹/۳۰ ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۳۸</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سبد_تدبیر 🏛️ سبدگردان تدبیر 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۲۲:۱۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 54 views 15:54 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Attachment.aspx?LetterSerial=7oGwQKFTHYOOObOOO5hgRHJ5cC8A%3d%3d</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=CemFgWQQQaQQQtAtAoiBU77x1BZg%3d%3d&amp;rt=2&amp;let=6&amp;ct=6&amp;ft=-1</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>بورس‌تریدر</t>
+          <t>تلگرام بورس‌تریدر</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>https://bourse-trader.ir/index.php?task=codal-reports</t>
+          <t>https://t.me/codalboursetrader/247606</t>
         </is>
       </c>
     </row>
@@ -11518,17 +11432,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>افشای اطلاعات بااهمیت - (برگزاری مزایده - گروه ب) منتهی به سال مالی ۱۴۰۵/۰۹/۳۰</t>
+          <t>صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) (شرکت توسعه تجارت داتام)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>واتی</t>
+          <t>وزمین</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1405/09/30</t>
+          <t>1404/12/29</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -11545,12 +11459,12 @@
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2 واتی گروه سرمایه گذاری آتیه دماوند لینک سابقه معاملات واتی ریز معاملات امروز واتی سهامداران عمده واتی افزایش سرمایه واتی تعدیل قیمت واتی تابلو عرضه و تقاضا صورتهای مالی نسبتهای مالی رتبه بندی بنیادی واتی اندیکاتورها واتی در TSETMC واتی در کدال ن-۲۰ افشای اطلاعات بااهمیت - (برگزاری مزایده - گروه ب) منتهی به سال مالی ۱۴۰۵/۰۹/۳۰</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #وزمین 🏛️ بانک ایران زمین 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) (شرکت توسعه تجارت داتام) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۵۴:۴۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 1 view 13:27 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=7oGwQKFTHYOOObOOO5hgRHJ5cC8A%3d%3d&amp;rt=2&amp;let=11&amp;ct=0&amp;ft=-1</t>
+          <t>https://codal.ir/Reports/Decision.aspx?LetterSerial=JBsqvslfTvARtL61f2Wg9w%3d%3d&amp;rt=0&amp;let=6&amp;ct=0&amp;ft=-1</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -11560,158 +11474,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>https://bourse-trader.ir/index.php?task=codal-reports؛ https://t.me/codalboursetrader/247765</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>گزارش کدال</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr"/>
-      <c r="C41" s="2" t="inlineStr"/>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>1405/07/21</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>صورت‌های مالی/حسابرسی</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>صورت های مالی؛ صورت‌های مالی</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>5 ولملت واسپاری ملت لینک سابقه معاملات ولملت ریز معاملات امروز ولملت سهامداران عمده ولملت افزایش سرمایه ولملت تعدیل قیمت ولملت تابلو عرضه و تقاضا صورتهای مالی نسبتهای مالی رتبه بندی بنیادی ولملت اندیکاتورها ولملت در TSETMC ولملت در کدال توقف نماد معاملاتی ناشر به استناد ماده ۱۹ مکرر/ ۱۲ مکرر ۳دستورالعمل اجرایی نحوه انجام معاملات ۱۴۰۵/۰۷/۲۱ ۱۶:۴۲:۳۰</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>https://codal.ir/Reports/Attachment.aspx?LetterSerial=K262scVeIjiNRrMfOOObOOOgvquQ%3d%3d</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>بورس‌تریدر</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>https://bourse-trader.ir/index.php?task=codal-reports</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>گزارش کدال</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr"/>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>1405/07/21</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>صورت‌های مالی/حسابرسی</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>صورت های مالی؛ صورت‌های مالی</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>3 پاسا ایران یاسا تایر و رابر لینک سابقه معاملات پاسا ریز معاملات امروز پاسا سهامداران عمده پاسا افزایش سرمایه پاسا تعدیل قیمت پاسا تابلو عرضه و تقاضا صورتهای مالی نسبتهای مالی رتبه بندی بنیادی پاسا اندیکاتورها پاسا در TSETMC پاسا در کدال مشخصات کمیته ریسک ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۳۲</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>https://codal.ir/Reports/Attachment.aspx?LetterSerial=1VmkDbw3qGy6TeKjT0burw%3d%3d</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>بورس‌تریدر</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>https://bourse-trader.ir/index.php?task=codal-reports</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>گزارش کدال</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>صورت وضعیت پورتفوی صندوق سرمایه گذاری دوره ۱ ماهه منتهی به ۱۴۰۵/۰۷/۱۵</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>آسود</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>1405/07/15</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>صورت‌های مالی/حسابرسی</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>صورت های مالی؛ صورت‌های مالی</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>4 آسود نهال آرمان اقتصاد لینک سابقه معاملات آسود ریز معاملات امروز آسود سهامداران عمده آسود افزایش سرمایه آسود تعدیل قیمت آسود تابلو عرضه و تقاضا صورتهای مالی نسبتهای مالی رتبه بندی بنیادی آسود اندیکاتورها آسود در TSETMC آسود در کدال صورت وضعیت پورتفوی صندوق سرمایه گذاری دوره ۱ ماهه منتهی به ۱۴۰۵/۰۷/۱۵ ۱۴۰۵/۰۷/۲۱ ۱۶:۴۳:۵۷</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>https://codal.ir/Reports/Attachment.aspx?LetterSerial=7amx5sjE6A0o4pFPOBbvzw%3d%3d</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>بورس‌تریدر؛ تلگرام بورس‌تریدر</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>https://bourse-trader.ir/index.php?task=codal-reports؛ https://t.me/codalboursetrader/247763</t>
+          <t>https://bourse-trader.ir/index.php?task=codal-reports؛ https://t.me/codalboursetrader/247767</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L43"/>
+  <autoFilter ref="A1:L40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11774,12 +11542,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>247747</t>
+          <t>247748</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:39:05+00:00</t>
+          <t>2026-10-13T12:42:03+00:00</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -11795,24 +11563,24 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #غدشت 🏛️ فرآورده های غذایی دشت مرغاب 📌 #خلاصه_تصمیمات_مجمع_عمومی_عادی_سالیانه 📋 خلاصه تصمیمات مجمع عمومی عادی سالیانه دوره ۱۲ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۰۷:۵۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 12:39 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #خیمن 🏛️ ایمن خودرو شرق 📌 #لغو_آگهی_ (اطلاعیه)_دعوت_به_مجمع_عمومی 📋 لغو آگهی (اطلاعیه) دعوت به مجمع عمومی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۰۹:۳۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 12:42 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247747</t>
+          <t>https://t.me/codalboursetrader/247748</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>247748</t>
+          <t>247749</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:42:03+00:00</t>
+          <t>2026-10-13T12:42:04+00:00</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -11828,24 +11596,24 @@
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #خیمن 🏛️ ایمن خودرو شرق 📌 #لغو_آگهی_ (اطلاعیه)_دعوت_به_مجمع_عمومی 📋 لغو آگهی (اطلاعیه) دعوت به مجمع عمومی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۰۹:۳۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 12:42 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آرمان_اندیش_بازار 🏛️ صندوق اختصاصی بازارگردانی آرمان اندیش 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۱۰:۱۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 14 views 12:42 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247748</t>
+          <t>https://t.me/codalboursetrader/247749</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>247749</t>
+          <t>247750</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:42:04+00:00</t>
+          <t>2026-10-13T12:48:03+00:00</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -11861,24 +11629,24 @@
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آرمان_اندیش_بازار 🏛️ صندوق اختصاصی بازارگردانی آرمان اندیش 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۱۰:۱۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 12:42 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #غدشت 🏛️ فرآورده های غذایی دشت مرغاب 📌 #خلاصه_تصمیمات_مجمع_عمومی_عادی_سالیانه 📋 خلاصه تصمیمات مجمع عمومی فوق العاده دوره ۱۲ ماهه منتهی به ۱۴۰۶/۰۳/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۱۶:۱۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 12:48 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247749</t>
+          <t>https://t.me/codalboursetrader/247750</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>247750</t>
+          <t>247751</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:48:03+00:00</t>
+          <t>2026-10-13T12:54:06+00:00</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -11894,24 +11662,24 @@
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #غدشت 🏛️ فرآورده های غذایی دشت مرغاب 📌 #خلاصه_تصمیمات_مجمع_عمومی_عادی_سالیانه 📋 خلاصه تصمیمات مجمع عمومی فوق العاده دوره ۱۲ ماهه منتهی به ۱۴۰۶/۰۳/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۱۶:۱۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 11 views 12:48 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تپسی 🏛️ پیشگامان فن آوری و دانش آرامیس 📌 #مشخصات_کمیته_حسابرسی_و_واحد_حسابرسی_داخلی 📋 مشخصات کمیته حسابرسی و واحد حسابرسی داخلی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۲۲:۳۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 11 views 12:54 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247750</t>
+          <t>https://t.me/codalboursetrader/247751</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>247751</t>
+          <t>247752</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:54:06+00:00</t>
+          <t>2026-10-13T12:57:04+00:00</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -11927,24 +11695,24 @@
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تپسی 🏛️ پیشگامان فن آوری و دانش آرامیس 📌 #مشخصات_کمیته_حسابرسی_و_واحد_حسابرسی_داخلی 📋 مشخصات کمیته حسابرسی و واحد حسابرسی داخلی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۲۲:۳۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 11 views 12:54 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 توضیحات در خصوص اطلاعات و صورت های مالی منتشر شده 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۲۴:۴۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 11 views 12:57 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247751</t>
+          <t>https://t.me/codalboursetrader/247752</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>247752</t>
+          <t>247753</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:57:04+00:00</t>
+          <t>2026-10-13T12:57:05+00:00</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -11960,24 +11728,24 @@
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 توضیحات در خصوص اطلاعات و صورت های مالی منتشر شده 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۲۴:۴۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 11 views 12:57 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کفرآور 🏛️ فرآورده های سیمان شرق 📌 #گزارش_فعالیت_هیئت_مدیره 📋 گزارش فعالیت هیئت مدیره دوره ۱۲ ماهه منتهی به ۱۴۰۵/۰۵/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۲۶:۴۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 11 views 12:57 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247752</t>
+          <t>https://t.me/codalboursetrader/247753</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>247753</t>
+          <t>247754</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:57:05+00:00</t>
+          <t>2026-10-13T13:00:03+00:00</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -11993,24 +11761,24 @@
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کفرآور 🏛️ فرآورده های سیمان شرق 📌 #گزارش_فعالیت_هیئت_مدیره 📋 گزارش فعالیت هیئت مدیره دوره ۱۲ ماهه منتهی به ۱۴۰۵/۰۵/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۲۶:۴۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 11 views 12:57 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سینرژی 🏛️ مبتنی بر کالای فارابی 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۲۸:۴۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 11 views 13:00 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247753</t>
+          <t>https://t.me/codalboursetrader/247754</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>247754</t>
+          <t>247755</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T13:00:03+00:00</t>
+          <t>2026-10-13T13:03:05+00:00</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -12026,24 +11794,24 @@
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سینرژی 🏛️ مبتنی بر کالای فارابی 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۲۸:۴۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 11 views 13:00 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #مادیرا 🏛️ گروه مادیران 📌 #گزارش_فعالیت_هیئت_مدیره 📋 گزارش فعالیت هیئت مدیره دوره ۱۲ ماهه منتهی به ۱۴۰۵/۰۳/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۳۱:۵۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 11 views 13:03 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247754</t>
+          <t>https://t.me/codalboursetrader/247755</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>247755</t>
+          <t>247756</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T13:03:05+00:00</t>
+          <t>2026-10-13T13:06:05+00:00</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -12059,19 +11827,19 @@
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #مادیرا 🏛️ گروه مادیران 📌 #گزارش_فعالیت_هیئت_مدیره 📋 گزارش فعالیت هیئت مدیره دوره ۱۲ ماهه منتهی به ۱۴۰۵/۰۳/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۳۱:۵۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 11 views 13:03 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #فنوال 🏛️ گروه کارخانه های تولیدی نورد الومینیوم 📌 #پیشنهاد_هیئت_مدیره_به_مجمع_عمومی_فوق_العاده_در_خصوص_افزایش_سرمایه 📋 پیشنهاد هیئت مدیره به مجمع عمومی فوق العاده در خصوص افزایش سرمایه(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۳۳:۱۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 8 views 13:06 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247755</t>
+          <t>https://t.me/codalboursetrader/247756</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>247756</t>
+          <t>247757</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -12086,30 +11854,30 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #فنوال 🏛️ گروه کارخانه های تولیدی نورد الومینیوم 📌 #پیشنهاد_هیئت_مدیره_به_مجمع_عمومی_فوق_العاده_در_خصوص_افزایش_سرمایه 📋 پیشنهاد هیئت مدیره به مجمع عمومی فوق العاده در خصوص افزایش سرمایه(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۳۳:۱۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 8 views 13:06 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ستران 🏛️ سیمان تهران 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۴/۳۱ (حسابرسی شده) (شرکت صنایع سیمان گیلان سبز) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۳۴:۵۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 9 views 13:06 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247756</t>
+          <t>https://t.me/codalboursetrader/247757</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>247757</t>
+          <t>247758</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T13:06:05+00:00</t>
+          <t>2026-10-13T13:09:05+00:00</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -12119,30 +11887,30 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ستران 🏛️ سیمان تهران 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۴/۳۱ (حسابرسی شده) (شرکت صنایع سیمان گیلان سبز) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۳۴:۵۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 9 views 13:06 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پاسا 🏛️ ایران یاسا تایر و رابر 📌 #مشخصات_کمیته_حسابرسی_و_واحد_حسابرسی_داخلی 📋 مشخصات کمیته حسابرسی و واحد حسابرسی داخلی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۳۷:۳۶ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 4 views 13:09 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247757</t>
+          <t>https://t.me/codalboursetrader/247758</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>247758</t>
+          <t>247759</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T13:09:05+00:00</t>
+          <t>2026-10-13T13:12:06+00:00</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -12158,24 +11926,24 @@
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پاسا 🏛️ ایران یاسا تایر و رابر 📌 #مشخصات_کمیته_حسابرسی_و_واحد_حسابرسی_داخلی 📋 مشخصات کمیته حسابرسی و واحد حسابرسی داخلی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۳۷:۳۶ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 4 views 13:09 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سپهر_بازار 🏛️ اختصاصی بازارگردانی سپهر بازار سرمایه 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۰:۲۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 5 views 13:12 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247758</t>
+          <t>https://t.me/codalboursetrader/247759</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>247759</t>
+          <t>247760</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T13:12:06+00:00</t>
+          <t>2026-10-13T13:12:07+00:00</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -12185,30 +11953,30 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سپهر_بازار 🏛️ اختصاصی بازارگردانی سپهر بازار سرمایه 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۰:۲۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 5 views 13:12 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #افران 🏛️ افرا نماد پایدار 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۵/۰۵/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۱:۲۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 6 views 13:12 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247759</t>
+          <t>https://t.me/codalboursetrader/247760</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>247760</t>
+          <t>247761</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T13:12:07+00:00</t>
+          <t>2026-10-13T13:15:05+00:00</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -12218,30 +11986,30 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #افران 🏛️ افرا نماد پایدار 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۵/۰۵/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۱:۲۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 6 views 13:12 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پاسا 🏛️ ایران یاسا تایر و رابر 📋 کمیته انتصابات 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۲:۲۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 5 views 13:15 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247760</t>
+          <t>https://t.me/codalboursetrader/247761</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>247761</t>
+          <t>247762</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T13:15:05+00:00</t>
+          <t>2026-10-13T13:15:06+00:00</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -12257,24 +12025,24 @@
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پاسا 🏛️ ایران یاسا تایر و رابر 📋 کمیته انتصابات 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۲:۲۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 5 views 13:15 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ولملت 🏛️ واسپاری ملت 📋 توقف نماد معاملاتی ناشر به استناد ماده ۱۹ مکرر/ ۱۲ مکرر ۳دستورالعمل اجرایی نحوه انجام معاملات 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۲:۳۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 5 views 13:15 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247761</t>
+          <t>https://t.me/codalboursetrader/247762</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>247762</t>
+          <t>247763</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T13:15:06+00:00</t>
+          <t>2026-10-13T13:15:07+00:00</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -12290,24 +12058,24 @@
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ولملت 🏛️ واسپاری ملت 📋 توقف نماد معاملاتی ناشر به استناد ماده ۱۹ مکرر/ ۱۲ مکرر ۳دستورالعمل اجرایی نحوه انجام معاملات 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۲:۳۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 5 views 13:15 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آسود 🏛️ نهال آرمان اقتصاد 📋 صورت وضعیت پورتفوی صندوق سرمایه گذاری دوره ۱ ماهه منتهی به ۱۴۰۵/۰۷/۱۵ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۳:۵۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 4 views 13:15 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247762</t>
+          <t>https://t.me/codalboursetrader/247763</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>247763</t>
+          <t>247764</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T13:15:07+00:00</t>
+          <t>2026-10-13T13:18:08+00:00</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -12323,24 +12091,24 @@
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آسود 🏛️ نهال آرمان اقتصاد 📋 صورت وضعیت پورتفوی صندوق سرمایه گذاری دوره ۱ ماهه منتهی به ۱۴۰۵/۰۷/۱۵ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۳:۵۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 4 views 13:15 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پاسا 🏛️ ایران یاسا تایر و رابر 📋 مشخصات کمیته ریسک 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۳۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 4 views 13:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247763</t>
+          <t>https://t.me/codalboursetrader/247764</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>247764</t>
+          <t>247765</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T13:18:08+00:00</t>
+          <t>2026-10-13T13:18:09+00:00</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -12356,24 +12124,24 @@
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پاسا 🏛️ ایران یاسا تایر و رابر 📋 مشخصات کمیته ریسک 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۳۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 4 views 13:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #واتی 🏛️ گروه سرمایه گذاری آتیه دماوند 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (برگزاری مزایده - گروه ب) منتهی به سال مالی ۱۴۰۵/۰۹/۳۰ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۳۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 4 views 13:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247764</t>
+          <t>https://t.me/codalboursetrader/247765</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>247765</t>
+          <t>247766</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T13:18:09+00:00</t>
+          <t>2026-10-13T13:18:10+00:00</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -12389,24 +12157,24 @@
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #واتی 🏛️ گروه سرمایه گذاری آتیه دماوند 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (برگزاری مزایده - گروه ب) منتهی به سال مالی ۱۴۰۵/۰۹/۳۰ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۳۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 4 views 13:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پارند_ثابت 🏛️ صندوق سرمایه گذاری پارند پایدار سپهر(ETF) 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۴۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 4 views 13:18 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247765</t>
+          <t>https://t.me/codalboursetrader/247766</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>247766</t>
+          <t>247767</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T13:18:10+00:00</t>
+          <t>2026-10-13T13:27:04+00:00</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -12416,30 +12184,30 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پارند_ثابت 🏛️ صندوق سرمایه گذاری پارند پایدار سپهر(ETF) 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۴۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 4 views 13:18 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #وزمین 🏛️ بانک ایران زمین 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) (شرکت توسعه تجارت داتام) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۵۴:۴۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 1 view 13:27 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247766</t>
+          <t>https://t.me/codalboursetrader/247767</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>247726</t>
+          <t>247727</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:36:04+00:00</t>
+          <t>2026-10-13T11:42:03+00:00</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -12455,24 +12223,24 @@
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📋 کمیته انتصابات 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۰۳:۵۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 14 views 11:36 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #افتخار_بازار 🏛️ اختصاصی بازارگردانی افتخار حافظ 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۱۰:۱۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 10 views 11:42 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247726</t>
+          <t>https://t.me/codalboursetrader/247727</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>247727</t>
+          <t>247728</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:42:03+00:00</t>
+          <t>2026-10-13T11:45:05+00:00</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -12488,24 +12256,24 @@
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #افتخار_بازار 🏛️ اختصاصی بازارگردانی افتخار حافظ 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۱۰:۱۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 10 views 11:42 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #فافق 🏛️ صنایع مس افق کرمان 📌 #معرفی /تغییر_در_ترکیب_اعضای_هیئت _مدیره 📋 معرفی /تغییر در ترکیب اعضای هیئت مدیره/مدیر عامل(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۱۴:۱۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 9 views 11:45 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247727</t>
+          <t>https://t.me/codalboursetrader/247728</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>247728</t>
+          <t>247729</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:45:05+00:00</t>
+          <t>2026-10-13T11:48:04+00:00</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -12521,24 +12289,24 @@
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #فافق 🏛️ صنایع مس افق کرمان 📌 #معرفی /تغییر_در_ترکیب_اعضای_هیئت _مدیره 📋 معرفی /تغییر در ترکیب اعضای هیئت مدیره/مدیر عامل(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۱۴:۱۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 9 views 11:45 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آرتان 🏛️ در سهام آرتان 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۱۵:۲۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 8 views 11:48 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247728</t>
+          <t>https://t.me/codalboursetrader/247729</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>247729</t>
+          <t>247730</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:48:04+00:00</t>
+          <t>2026-10-13T11:54:03+00:00</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -12554,24 +12322,24 @@
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آرتان 🏛️ در سهام آرتان 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۱۵:۲۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 8 views 11:48 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #حافظ_سهام 🏛️ صندوق سرمایه گذاری مشترک کارگزاری حافظ 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۲۲:۰۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 9 views 11:54 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247729</t>
+          <t>https://t.me/codalboursetrader/247730</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>247730</t>
+          <t>247731</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:54:03+00:00</t>
+          <t>2026-10-13T11:54:04+00:00</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -12581,30 +12349,30 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #حافظ_سهام 🏛️ صندوق سرمایه گذاری مشترک کارگزاری حافظ 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۲۲:۰۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 8 views 11:54 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #واعتماد 🏛️ سرمایه گذاری توسعه اعتماد 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ (حسابرسی نشده)(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۲۲:۳۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 9 views 11:54 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247730</t>
+          <t>https://t.me/codalboursetrader/247731</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>247731</t>
+          <t>247732</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:54:04+00:00</t>
+          <t>2026-10-13T12:06:03+00:00</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -12614,30 +12382,30 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #واعتماد 🏛️ سرمایه گذاری توسعه اعتماد 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ (حسابرسی نشده)(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۲۲:۳۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 8 views 11:54 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #دبالک 🏛️ تولید مواد اولیه داروئی البرز بالک 📌 #معرفی /تغییر_در_ترکیب_اعضای_هیئت _مدیره 📋 معرفی /تغییر در ترکیب اعضای هیئت مدیره/مدیر عامل 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۳۳:۲۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 5 views 12:06 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247731</t>
+          <t>https://t.me/codalboursetrader/247732</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>247732</t>
+          <t>247733</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:06:03+00:00</t>
+          <t>2026-10-13T12:06:04+00:00</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -12653,24 +12421,24 @@
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #دبالک 🏛️ تولید مواد اولیه داروئی البرز بالک 📌 #معرفی /تغییر_در_ترکیب_اعضای_هیئت _مدیره 📋 معرفی /تغییر در ترکیب اعضای هیئت مدیره/مدیر عامل 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۳۳:۲۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 5 views 12:06 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #حافظ_سهام 🏛️ صندوق سرمایه گذاری مشترک کارگزاری حافظ 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۳۴:۴۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 12:06 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247732</t>
+          <t>https://t.me/codalboursetrader/247733</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>247733</t>
+          <t>247734</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:06:04+00:00</t>
+          <t>2026-10-13T12:06:05+00:00</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -12686,24 +12454,24 @@
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #حافظ_سهام 🏛️ صندوق سرمایه گذاری مشترک کارگزاری حافظ 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۳۴:۴۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 12:06 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شپترو 🏛️ پتروشیمی آبادان 📋 مشخصات کمیته ریسک 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۳۵:۱۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 12:06 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247733</t>
+          <t>https://t.me/codalboursetrader/247734</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>247734</t>
+          <t>247735</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:06:05+00:00</t>
+          <t>2026-10-13T12:09:05+00:00</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -12719,24 +12487,24 @@
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شپترو 🏛️ پتروشیمی آبادان 📋 مشخصات کمیته ریسک 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۳۵:۱۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 12:06 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سرآمد_بازار 🏛️ اختصاصی بازارگردانی الگوریتم سرآمد بازار 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۳۷:۱۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 11 views 12:09 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247734</t>
+          <t>https://t.me/codalboursetrader/247735</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>247735</t>
+          <t>247736</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:09:05+00:00</t>
+          <t>2026-10-13T12:12:07+00:00</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -12746,30 +12514,30 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سرآمد_بازار 🏛️ اختصاصی بازارگردانی الگوریتم سرآمد بازار 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۳۷:۱۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 11 views 12:09 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آلا 🏛️ اعتماد ارغوان 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۴۱:۳۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 12:12 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247735</t>
+          <t>https://t.me/codalboursetrader/247736</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>247736</t>
+          <t>247737</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:12:07+00:00</t>
+          <t>2026-10-13T12:15:04+00:00</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -12779,30 +12547,30 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آلا 🏛️ اعتماد ارغوان 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۴۱:۳۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 12:12 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سیسکو 🏛️ فولاد سیرجان ایرانیان 📋 مدارک انتشار اوراق مرابحه شرکت واسط مالی مرداد پنجم (با مسئولیت محدود) به منظور تأمین مالی شرکت فولاد سیرجان ایرانیان (سهامی عام) (به پیوست) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۴۲:۰۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 14 views 12:15 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247736</t>
+          <t>https://t.me/codalboursetrader/247737</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>247737</t>
+          <t>247738</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:15:04+00:00</t>
+          <t>2026-10-13T12:15:05+00:00</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -12812,30 +12580,30 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سیسکو 🏛️ فولاد سیرجان ایرانیان 📋 مدارک انتشار اوراق مرابحه شرکت واسط مالی مرداد پنجم (با مسئولیت محدود) به منظور تأمین مالی شرکت فولاد سیرجان ایرانیان (سهامی عام) (به پیوست) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۴۲:۰۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 14 views 12:15 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ثنا 🏛️ زرین نهال ثنا 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۴۲:۰۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 12:15 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247737</t>
+          <t>https://t.me/codalboursetrader/247738</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>247738</t>
+          <t>247739</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:15:05+00:00</t>
+          <t>2026-10-13T12:15:06+00:00</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -12845,30 +12613,30 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ثنا 🏛️ زرین نهال ثنا 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۴۲:۰۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 16 views 12:15 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تکیمیا 🏛️ تامین سرمایه کیمیا 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - تعهد پذیره نویسی و بازارگردانی اوراق دایو پارس- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۴۴:۵۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 12:15 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247738</t>
+          <t>https://t.me/codalboursetrader/247739</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>247739</t>
+          <t>247740</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:15:06+00:00</t>
+          <t>2026-10-13T12:18:12+00:00</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -12884,24 +12652,24 @@
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تکیمیا 🏛️ تامین سرمایه کیمیا 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - تعهد پذیره نویسی و بازارگردانی اوراق دایو پارس- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۴۴:۵۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 12:15 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #بکابل 🏛️ سیم و کابل ابهر 📌 #پیشنهاد_هیئت_مدیره_به_مجمع_عمومی_فوق_العاده_در_خصوص_افزایش_سرمایه 📋 پیشنهاد هیئت مدیره به مجمع عمومی فوق العاده در خصوص افزایش سرمایه 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۴۵:۱۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 14 views 12:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247739</t>
+          <t>https://t.me/codalboursetrader/247740</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>247740</t>
+          <t>247741</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:18:12+00:00</t>
+          <t>2026-10-13T12:21:09+00:00</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -12917,24 +12685,24 @@
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #بکابل 🏛️ سیم و کابل ابهر 📌 #پیشنهاد_هیئت_مدیره_به_مجمع_عمومی_فوق_العاده_در_خصوص_افزایش_سرمایه 📋 پیشنهاد هیئت مدیره به مجمع عمومی فوق العاده در خصوص افزایش سرمایه 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۴۵:۱۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 12:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #غچین 🏛️ مجتمع کشت و صنعت چین چین 📌 #گزارش_کنترل_داخلی 📋 گزارش کنترل های داخلی در تاریخ ۱۴۰۵/۰۳/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۴۹:۴۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 12:21 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247740</t>
+          <t>https://t.me/codalboursetrader/247741</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>247741</t>
+          <t>247742</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:21:09+00:00</t>
+          <t>2026-10-13T12:21:10+00:00</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -12950,24 +12718,24 @@
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #غچین 🏛️ مجتمع کشت و صنعت چین چین 📌 #گزارش_کنترل_داخلی 📋 گزارش کنترل های داخلی در تاریخ ۱۴۰۵/۰۳/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۴۹:۴۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 16 views 12:21 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سفارس 🏛️ سیمان فارس و خوزستان 📌 #آگهی_ثبت_تصمیمات_مجمع_عادی_سالیانه 📋 آگهی ثبت تصمیمات مجمع عادی سالیانه دوره ۱۲ ماهه منتهی به ۱۴۰۵/۰۲/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۵۱:۰۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 12:21 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247741</t>
+          <t>https://t.me/codalboursetrader/247742</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>247742</t>
+          <t>247743</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:21:10+00:00</t>
+          <t>2026-10-13T12:24:04+00:00</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -12983,24 +12751,24 @@
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سفارس 🏛️ سیمان فارس و خوزستان 📌 #آگهی_ثبت_تصمیمات_مجمع_عادی_سالیانه 📋 آگهی ثبت تصمیمات مجمع عادی سالیانه دوره ۱۲ ماهه منتهی به ۱۴۰۵/۰۲/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۵۱:۰۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 16 views 12:21 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #غپاک 🏛️ لبنیات پاستوریزه پاک 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - لغو مزایده فروش زمین زرنان- گروه ب) منتهی به سال مالی ۱۴۰۶/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۵۱:۰۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 12:24 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247742</t>
+          <t>https://t.me/codalboursetrader/247743</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>247743</t>
+          <t>247744</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:24:04+00:00</t>
+          <t>2026-10-13T12:24:05+00:00</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -13016,24 +12784,24 @@
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #غپاک 🏛️ لبنیات پاستوریزه پاک 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - لغو مزایده فروش زمین زرنان- گروه ب) منتهی به سال مالی ۱۴۰۶/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۵۱:۰۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 12:24 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #فارابی_بازار 🏛️ صندوق سرمایه گذاری اختصاصی بازارگردانی الگوریتمی امید فارابی 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۷/۲۲ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۵۱:۴۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 16 views 12:24 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247743</t>
+          <t>https://t.me/codalboursetrader/247744</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>247744</t>
+          <t>247745</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:24:05+00:00</t>
+          <t>2026-10-13T12:30:08+00:00</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -13049,24 +12817,24 @@
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #فارابی_بازار 🏛️ صندوق سرمایه گذاری اختصاصی بازارگردانی الگوریتمی امید فارابی 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۷/۲۲ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۵۱:۴۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 16 views 12:24 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سینا_بازار 🏛️ اختصاصی بازارگردانی سینا 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۵۷:۰۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 12:30 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247744</t>
+          <t>https://t.me/codalboursetrader/247745</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>247745</t>
+          <t>247746</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T12:30:08+00:00</t>
+          <t>2026-10-13T12:33:07+00:00</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -13082,24 +12850,24 @@
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سینا_بازار 🏛️ اختصاصی بازارگردانی سینا 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۵۷:۰۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 12:30 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #خکار 🏛️ ایرکا پارت صنعت 📌 #پیشنهاد_هیئت_مدیره_به_مجمع_عمومی_فوق_العاده_در_خصوص_افزایش_سرمایه 📋 پیشنهاد هیئت مدیره به مجمع عمومی فوق العاده در خصوص افزایش سرمایه 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۰۱:۰۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 12:33 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247745</t>
+          <t>https://t.me/codalboursetrader/247746</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>247705</t>
+          <t>247706</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:42:06+00:00</t>
+          <t>2026-10-13T10:42:07+00:00</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -13112,31 +12880,27 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>بهره برداری؛ بهره‌برداری</t>
-        </is>
-      </c>
+      <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تبرک 🏛️ گروه کارخانجات صنعتی تبرک 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - اجازه بهره برداری- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۰۹:۵۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 21 views 10:42 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ثقزوی 🏛️ توسعه عمران و سازندگی ایرانیان نوآور 📋 کمیته انتصابات(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۱۱:۴۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 25 views 10:42 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247705</t>
+          <t>https://t.me/codalboursetrader/247706</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>247706</t>
+          <t>247707</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:42:07+00:00</t>
+          <t>2026-10-13T10:45:07+00:00</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -13146,30 +12910,30 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ثقزوی 🏛️ توسعه عمران و سازندگی ایرانیان نوآور 📋 کمیته انتصابات(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۱۱:۴۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 25 views 10:42 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #وپاسار 🏛️ بانک پاسارگاد 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) (شرکت مدیریت ساختمانی آریان پاسارگاد) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۱۳:۱۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 25 views 10:45 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247706</t>
+          <t>https://t.me/codalboursetrader/247707</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>247707</t>
+          <t>247708</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:45:07+00:00</t>
+          <t>2026-10-13T10:45:08+00:00</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -13179,30 +12943,30 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #وپاسار 🏛️ بانک پاسارگاد 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) (شرکت مدیریت ساختمانی آریان پاسارگاد) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۱۳:۱۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 25 views 10:45 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #فافزا 🏛️ فولاد افزا سپاهان 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - افزایش نرخ دولومیت داخلی بدلیل افزایش کرایه حمل- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۱۳:۴۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 10:45 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247707</t>
+          <t>https://t.me/codalboursetrader/247708</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>247708</t>
+          <t>247709</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:45:08+00:00</t>
+          <t>2026-10-13T10:54:06+00:00</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -13218,24 +12982,24 @@
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #فافزا 🏛️ فولاد افزا سپاهان 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - افزایش نرخ دولومیت داخلی بدلیل افزایش کرایه حمل- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۱۳:۴۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 10:45 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #حفاری 🏛️ حفاری شمال 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (تغییر در مفاد هر نوع اطلاعیه بااهمیتی که قبلاً منتشر شده است - گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۲۲:۲۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 10:54 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247708</t>
+          <t>https://t.me/codalboursetrader/247709</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>247709</t>
+          <t>247710</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:54:06+00:00</t>
+          <t>2026-10-13T10:57:04+00:00</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -13245,30 +13009,30 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #حفاری 🏛️ حفاری شمال 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (تغییر در مفاد هر نوع اطلاعیه بااهمیتی که قبلاً منتشر شده است - گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۲۲:۲۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 10:54 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تلاشگستران_آینده 🏛️ تلاش گستران آینده 📌 #صورت_های_مالی_میان_دوره_ای 📋 مشمول اصل ۴۴ - صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۲۵:۴۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 19 views 10:57 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247709</t>
+          <t>https://t.me/codalboursetrader/247710</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>247710</t>
+          <t>247711</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:57:04+00:00</t>
+          <t>2026-10-13T11:00:10+00:00</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -13278,30 +13042,30 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تلاشگستران_آینده 🏛️ تلاش گستران آینده 📌 #صورت_های_مالی_میان_دوره_ای 📋 مشمول اصل ۴۴ - صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۲۵:۴۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 19 views 10:57 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📋 مشخصات کمیته ریسک 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۲۹:۳۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 11:00 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247710</t>
+          <t>https://t.me/codalboursetrader/247711</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>247711</t>
+          <t>247712</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:00:10+00:00</t>
+          <t>2026-10-13T11:00:11+00:00</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -13317,24 +13081,24 @@
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📋 مشخصات کمیته ریسک 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۲۹:۳۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 11:00 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آب 🏛️ مهندسی توسعه آب آسیا 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - آخرین وضعیت طرح های توسعه و مخارج انجام شده تاکنون- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۲۹:۳۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 19 views 11:00 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247711</t>
+          <t>https://t.me/codalboursetrader/247712</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>247712</t>
+          <t>247713</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:00:11+00:00</t>
+          <t>2026-10-13T11:03:08+00:00</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -13350,24 +13114,24 @@
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آب 🏛️ مهندسی توسعه آب آسیا 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - آخرین وضعیت طرح های توسعه و مخارج انجام شده تاکنون- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۲۹:۳۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 19 views 11:00 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سیمرغ 🏛️ سیمرغ 📋 مشخصات کمیته ریسک 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۳۰:۳۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 19 views 11:03 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247712</t>
+          <t>https://t.me/codalboursetrader/247713</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>247713</t>
+          <t>247714</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:03:08+00:00</t>
+          <t>2026-10-13T11:09:05+00:00</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -13377,30 +13141,34 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>راه اندازی؛ راه‌اندازی</t>
+        </is>
+      </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سیمرغ 🏛️ سیمرغ 📋 مشخصات کمیته ریسک 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۳۰:۳۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 19 views 11:03 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آتیه 🏛️ تامین آتیه کارکنان صنعت برق خراسان 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) (شرکت احداث وراه اندازی تاسیسات انرژی اتیه سناباد آرتا) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۳۷:۳۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 11:09 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247713</t>
+          <t>https://t.me/codalboursetrader/247714</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>247714</t>
+          <t>247715</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:09:05+00:00</t>
+          <t>2026-10-13T11:12:05+00:00</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -13413,31 +13181,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>راه اندازی؛ راه‌اندازی</t>
-        </is>
-      </c>
+      <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آتیه 🏛️ تامین آتیه کارکنان صنعت برق خراسان 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) (شرکت احداث وراه اندازی تاسیسات انرژی اتیه سناباد آرتا) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۳۷:۳۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 11:09 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آتیه 🏛️ تامین آتیه کارکنان صنعت برق خراسان 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) (شرکت کارگزاری رسمی بیمه آتیه گستر آرامش سناباد) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۳۹:۰۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 15 views 11:12 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247714</t>
+          <t>https://t.me/codalboursetrader/247715</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>247715</t>
+          <t>247716</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:12:05+00:00</t>
+          <t>2026-10-13T11:12:07+00:00</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -13453,24 +13217,24 @@
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آتیه 🏛️ تامین آتیه کارکنان صنعت برق خراسان 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) (شرکت کارگزاری رسمی بیمه آتیه گستر آرامش سناباد) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۳۹:۰۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 15 views 11:12 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آتیه 🏛️ تامین آتیه کارکنان صنعت برق خراسان 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) (شرکت خدمات بیمه ای آتیه صنعت برق شمس) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۴۰:۰۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 11:12 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247715</t>
+          <t>https://t.me/codalboursetrader/247716</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>247716</t>
+          <t>247717</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:12:07+00:00</t>
+          <t>2026-10-13T11:18:15+00:00</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -13480,30 +13244,30 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آتیه 🏛️ تامین آتیه کارکنان صنعت برق خراسان 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) (شرکت خدمات بیمه ای آتیه صنعت برق شمس) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۴۰:۰۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 11:12 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #درین 🏛️ درین آتا 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۲ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۴۶:۲۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 15 views 11:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247716</t>
+          <t>https://t.me/codalboursetrader/247717</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>247717</t>
+          <t>247718</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:18:15+00:00</t>
+          <t>2026-10-13T11:21:04+00:00</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -13519,24 +13283,24 @@
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #درین 🏛️ درین آتا 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۲ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۴۶:۲۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 15 views 11:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #فرابورس 🏛️ فرا بورس ایران 📌 #آگهی_دعوت_به_مجمع_عمومی_فوق_العاده 📋 آگهی دعوت به مجمع عمومی فوق العاده دوره ۱۲ ماهه منتهی به ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۴۸:۰۶ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 15 views 11:21 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247717</t>
+          <t>https://t.me/codalboursetrader/247718</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>247718</t>
+          <t>247719</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:21:04+00:00</t>
+          <t>2026-10-13T11:21:05+00:00</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -13552,24 +13316,24 @@
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #فرابورس 🏛️ فرا بورس ایران 📌 #آگهی_دعوت_به_مجمع_عمومی_فوق_العاده 📋 آگهی دعوت به مجمع عمومی فوق العاده دوره ۱۲ ماهه منتهی به ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۴۸:۰۶ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 15 views 11:21 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #مروارید 🏛️ مروارید آتا 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۲ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۵۰:۱۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 16 views 11:21 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247718</t>
+          <t>https://t.me/codalboursetrader/247719</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>247719</t>
+          <t>247720</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:21:05+00:00</t>
+          <t>2026-10-13T11:24:03+00:00</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -13579,30 +13343,30 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #مروارید 🏛️ مروارید آتا 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۲ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۵۰:۱۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 16 views 11:21 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پناه 🏛️ بخشی شایسته فردا 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۵/۰۵/۱۵ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۵۲:۱۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 11:24 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247719</t>
+          <t>https://t.me/codalboursetrader/247720</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>247720</t>
+          <t>247721</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:24:03+00:00</t>
+          <t>2026-10-13T11:24:04+00:00</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -13612,30 +13376,30 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پناه 🏛️ بخشی شایسته فردا 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۵/۰۵/۱۵ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۵۲:۱۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 11:24 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تابان_بازار 🏛️ اختصاصی بازارگردانی تابان 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۲ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۵۳:۱۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 11:24 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247720</t>
+          <t>https://t.me/codalboursetrader/247721</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>247721</t>
+          <t>247722</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:24:04+00:00</t>
+          <t>2026-10-13T11:27:06+00:00</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -13651,24 +13415,24 @@
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تابان_بازار 🏛️ اختصاصی بازارگردانی تابان 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۲ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۵۳:۱۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 11:24 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ولیز 🏛️ لیزینگ ایران 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - پرونده مطالباتی آقای مهدی میثاقی- گروه ب) منتهی به سال مالی ۱۴۰۵/۰۹/۳۰ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۵۵:۵۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 11:27 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247721</t>
+          <t>https://t.me/codalboursetrader/247722</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>247722</t>
+          <t>247723</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:27:06+00:00</t>
+          <t>2026-10-13T11:30:08+00:00</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -13684,24 +13448,24 @@
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ولیز 🏛️ لیزینگ ایران 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - پرونده مطالباتی آقای مهدی میثاقی- گروه ب) منتهی به سال مالی ۱۴۰۵/۰۹/۳۰ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۵۵:۵۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 11:27 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سدبیر 🏛️ سرمایه گذاری تدبیر گران فارس و خوزستان 📌 #تغییر_نشانی 📋 تغییر نشانی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۵۸:۲۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 11:30 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247722</t>
+          <t>https://t.me/codalboursetrader/247723</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>247723</t>
+          <t>247724</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:30:08+00:00</t>
+          <t>2026-10-13T11:30:09+00:00</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -13717,19 +13481,19 @@
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سدبیر 🏛️ سرمایه گذاری تدبیر گران فارس و خوزستان 📌 #تغییر_نشانی 📋 تغییر نشانی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۵۸:۲۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 11:30 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آرتان 🏛️ در سهام آرتان 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۷/۲۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۵۹:۳۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 14 views 11:30 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247723</t>
+          <t>https://t.me/codalboursetrader/247724</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>247724</t>
+          <t>247725</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -13744,30 +13508,30 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آرتان 🏛️ در سهام آرتان 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۷/۲۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۵۹:۳۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 14 views 11:30 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کی_ام_سی 🏛️ کرمان موتور 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۴/۰۷/۳۰ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۵۹:۳۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 14 views 11:30 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247724</t>
+          <t>https://t.me/codalboursetrader/247725</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>247684</t>
+          <t>247685</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T09:42:05+00:00</t>
+          <t>2026-10-13T09:45:05+00:00</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -13783,24 +13547,24 @@
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کاریزما_ثابت 🏛️ در اوراق بهادار با درآمد ثابت کاریزما 📋 تصمیمات مجمع صندوق سرمایه گذاری(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۱۱:۰۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 09:42 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کخاک 🏛️ صنایع خاک چینی ایران 📌 #اطلاعات_حاصل_از_برگزاری_کنفرانس_اطلاع_رسانی 📋 اطلاعات حاصل از برگزاری کنفرانس اطلاع رسانی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۱۴:۰۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 14 views 09:45 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247684</t>
+          <t>https://t.me/codalboursetrader/247685</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>247685</t>
+          <t>247686</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T09:45:05+00:00</t>
+          <t>2026-10-13T09:48:10+00:00</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -13816,24 +13580,24 @@
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کخاک 🏛️ صنایع خاک چینی ایران 📌 #اطلاعات_حاصل_از_برگزاری_کنفرانس_اطلاع_رسانی 📋 اطلاعات حاصل از برگزاری کنفرانس اطلاع رسانی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۱۴:۰۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 14 views 09:45 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کوثر_ثابت 🏛️ در اوراق بهادار با درآمد ثابت کوثر یکم 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۲ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۱۷:۰۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 09:48 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247685</t>
+          <t>https://t.me/codalboursetrader/247686</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>247686</t>
+          <t>247687</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T09:48:10+00:00</t>
+          <t>2026-10-13T09:48:11+00:00</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -13843,30 +13607,30 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کوثر_ثابت 🏛️ در اوراق بهادار با درآمد ثابت کوثر یکم 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۲ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۱۷:۰۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 09:48 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۱۷:۲۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 09:48 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247686</t>
+          <t>https://t.me/codalboursetrader/247687</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>247687</t>
+          <t>247688</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T09:48:11+00:00</t>
+          <t>2026-10-13T09:54:07+00:00</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -13882,24 +13646,24 @@
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۱۷:۲۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 09:48 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۵/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۲۲:۳۶ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 09:54 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247687</t>
+          <t>https://t.me/codalboursetrader/247688</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>247688</t>
+          <t>247689</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T09:54:07+00:00</t>
+          <t>2026-10-13T09:57:04+00:00</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -13915,24 +13679,24 @@
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۵/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۲۲:۳۶ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 09:54 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۴/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۲۵:۲۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 25 views 09:57 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247688</t>
+          <t>https://t.me/codalboursetrader/247689</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>247689</t>
+          <t>247690</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T09:57:04+00:00</t>
+          <t>2026-10-13T10:00:06+00:00</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -13948,24 +13712,24 @@
       <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۴/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۲۵:۲۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 25 views 09:57 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #هانیکو 🏛️ هامون نایزه 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۲۷:۱۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 27 views 10:00 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247689</t>
+          <t>https://t.me/codalboursetrader/247690</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>247690</t>
+          <t>247691</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:00:06+00:00</t>
+          <t>2026-10-13T10:06:04+00:00</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -13975,30 +13739,34 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>بهره برداری؛ بهره‌برداری</t>
+        </is>
+      </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #هانیکو 🏛️ هامون نایزه 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۲۷:۱۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 27 views 10:00 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #غبهار 🏛️ کشت و صنعت بهاران گلبهار خراسان 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - اجازه بهره برداری از برند- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۳۴:۲۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 24 views 10:06 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247690</t>
+          <t>https://t.me/codalboursetrader/247691</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>247691</t>
+          <t>247692</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:06:04+00:00</t>
+          <t>2026-10-13T10:12:07+00:00</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -14011,31 +13779,27 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>بهره برداری؛ بهره‌برداری</t>
-        </is>
-      </c>
+      <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #غبهار 🏛️ کشت و صنعت بهاران گلبهار خراسان 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - اجازه بهره برداری از برند- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۳۴:۲۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 24 views 10:06 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ومهان 🏛️ گروه توسعه مالی مهر آیندگان 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - مدارک و مستندات انتشار اوراق اختیار فروش تبعی- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۴۰:۰۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 10:12 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247691</t>
+          <t>https://t.me/codalboursetrader/247692</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>247692</t>
+          <t>247693</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:12:07+00:00</t>
+          <t>2026-10-13T10:15:04+00:00</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -14051,24 +13815,24 @@
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ومهان 🏛️ گروه توسعه مالی مهر آیندگان 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - مدارک و مستندات انتشار اوراق اختیار فروش تبعی- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۴۰:۰۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 10:12 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #امیران 🏛️ گروه سرمایه گذاری امیر 📋 مشخصات کمیته ریسک(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۴۴:۴۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 23 views 10:15 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247692</t>
+          <t>https://t.me/codalboursetrader/247693</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>247693</t>
+          <t>247694</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:15:04+00:00</t>
+          <t>2026-10-13T10:18:12+00:00</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -14084,24 +13848,24 @@
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #امیران 🏛️ گروه سرمایه گذاری امیر 📋 مشخصات کمیته ریسک(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۴۴:۴۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 23 views 10:15 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #میلاد_شهر_بازار 🏛️ اختصاصی بازارگردانی شاهین میلاد شهر 📋 لغو آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۷/۳۰ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۴۶:۴۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 19 views 10:18 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247693</t>
+          <t>https://t.me/codalboursetrader/247694</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>247694</t>
+          <t>247695</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:18:12+00:00</t>
+          <t>2026-10-13T10:18:13+00:00</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -14117,24 +13881,24 @@
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #میلاد_شهر_بازار 🏛️ اختصاصی بازارگردانی شاهین میلاد شهر 📋 لغو آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۷/۳۰ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۴۶:۴۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 19 views 10:18 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ثقزوی 🏛️ توسعه عمران و سازندگی ایرانیان نوآور 📋 کمیته انتصابات 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۴۸:۰۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 23 views 10:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247694</t>
+          <t>https://t.me/codalboursetrader/247695</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>247695</t>
+          <t>247696</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:18:13+00:00</t>
+          <t>2026-10-13T10:24:05+00:00</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -14150,24 +13914,24 @@
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ثقزوی 🏛️ توسعه عمران و سازندگی ایرانیان نوآور 📋 کمیته انتصابات 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۴۸:۰۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 23 views 10:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #میلاد_شهر_بازار 🏛️ اختصاصی بازارگردانی شاهین میلاد شهر 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۲ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۵۳:۱۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 19 views 10:24 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247695</t>
+          <t>https://t.me/codalboursetrader/247696</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>247696</t>
+          <t>247697</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:24:05+00:00</t>
+          <t>2026-10-13T10:27:04+00:00</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -14177,30 +13941,30 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #میلاد_شهر_بازار 🏛️ اختصاصی بازارگردانی شاهین میلاد شهر 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۲ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۵۳:۱۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 19 views 10:24 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #و_پایدار 🏛️ سرمایه گذاری توسعه اقتصاد پایدار سینا 📌 #گزارش_فعالیت_ماهانه_دوره_۱_ماهه 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۵۴:۳۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 10:27 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247696</t>
+          <t>https://t.me/codalboursetrader/247697</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>247697</t>
+          <t>247698</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:27:04+00:00</t>
+          <t>2026-10-13T10:30:04+00:00</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -14210,30 +13974,30 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #و_پایدار 🏛️ سرمایه گذاری توسعه اقتصاد پایدار سینا 📌 #گزارش_فعالیت_ماهانه_دوره_۱_ماهه 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۵۴:۳۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 10:27 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ثروت_خصوصی 🏛️ خصوصی ثروت آفرین فیروزه 📋 تصمیمات مجمع صندوق سرمایه گذاری(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۵۹:۱۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 20 views 10:30 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247697</t>
+          <t>https://t.me/codalboursetrader/247698</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>247698</t>
+          <t>247699</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:30:04+00:00</t>
+          <t>2026-10-13T10:33:05+00:00</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -14249,24 +14013,24 @@
       <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ثروت_خصوصی 🏛️ خصوصی ثروت آفرین فیروزه 📋 تصمیمات مجمع صندوق سرمایه گذاری(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۵۹:۱۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 20 views 10:30 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کرمان 🏛️ سرمایه گذاری توسعه و عمران استان کرمان 📌 #گزارش_کنترل_داخلی 📋 گزارش کنترل های داخلی در تاریخ ۱۴۰۵/۰۳/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۰۰:۲۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 10:33 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247698</t>
+          <t>https://t.me/codalboursetrader/247699</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>247699</t>
+          <t>247700</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:33:05+00:00</t>
+          <t>2026-10-13T10:33:06+00:00</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -14282,24 +14046,24 @@
       <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کرمان 🏛️ سرمایه گذاری توسعه و عمران استان کرمان 📌 #گزارش_کنترل_داخلی 📋 گزارش کنترل های داخلی در تاریخ ۱۴۰۵/۰۳/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۰۰:۲۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 10:33 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سیمرغ 🏛️ سیمرغ 📌 #مشخصات_کمیته_حسابرسی_و_واحد_حسابرسی_داخلی 📋 مشخصات کمیته حسابرسی و واحد حسابرسی داخلی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۰۳:۰۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 19 views 10:33 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247699</t>
+          <t>https://t.me/codalboursetrader/247700</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>247700</t>
+          <t>247701</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:33:06+00:00</t>
+          <t>2026-10-13T10:36:07+00:00</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -14315,24 +14079,24 @@
       <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سیمرغ 🏛️ سیمرغ 📌 #مشخصات_کمیته_حسابرسی_و_واحد_حسابرسی_داخلی 📋 مشخصات کمیته حسابرسی و واحد حسابرسی داخلی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۰۳:۰۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 19 views 10:33 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #وصنا 🏛️ سرمایه گذاری گروه صنایع بهشهر ایران 📌 #معرفی /تغییر_در_ترکیب_اعضای_هیئت _مدیره 📋 معرفی /تغییر در ترکیب اعضای هیئت مدیره/مدیر عامل 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۰۳:۵۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 21 views 10:36 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247700</t>
+          <t>https://t.me/codalboursetrader/247701</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>247701</t>
+          <t>247702</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:36:07+00:00</t>
+          <t>2026-10-13T10:36:08+00:00</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -14342,30 +14106,30 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #وصنا 🏛️ سرمایه گذاری گروه صنایع بهشهر ایران 📌 #معرفی /تغییر_در_ترکیب_اعضای_هیئت _مدیره 📋 معرفی /تغییر در ترکیب اعضای هیئت مدیره/مدیر عامل 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۰۳:۵۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 21 views 10:36 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #بمولد 🏛️ مولد نیروگاهی تجارت فارس 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۰۴:۰۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 10:36 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247701</t>
+          <t>https://t.me/codalboursetrader/247702</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>247702</t>
+          <t>247703</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:36:08+00:00</t>
+          <t>2026-10-13T10:39:04+00:00</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -14375,30 +14139,30 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #بمولد 🏛️ مولد نیروگاهی تجارت فارس 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۰۴:۰۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 10:36 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #قزوین 🏛️ کارخانجات قند قزوین 📌 #آگهی_ثبت_تصمیمات_مجمع_عادی_سالیانه 📋 آگهی ثبت تصمیمات مجمع عادی سالیانه دوره ۱۲ ماهه منتهی به ۱۴۰۴/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۰۸:۱۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 10:39 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247702</t>
+          <t>https://t.me/codalboursetrader/247703</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>247703</t>
+          <t>247704</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T10:39:04+00:00</t>
+          <t>2026-10-13T10:42:05+00:00</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -14414,24 +14178,24 @@
       <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #قزوین 🏛️ کارخانجات قند قزوین 📌 #آگهی_ثبت_تصمیمات_مجمع_عادی_سالیانه 📋 آگهی ثبت تصمیمات مجمع عادی سالیانه دوره ۱۲ ماهه منتهی به ۱۴۰۴/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۰۸:۱۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 10:39 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #بیوتیک 🏛️ آنتی بیوتیک سازی ایران 📌 #معرفی /تغییر_در_ترکیب_اعضای_هیئت _مدیره 📋 معرفی /تغییر در ترکیب اعضای هیئت مدیره/مدیر عامل(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۴:۰۹:۲۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 20 views 10:42 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247703</t>
+          <t>https://t.me/codalboursetrader/247704</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>247663</t>
+          <t>247664</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T08:09:07+00:00</t>
+          <t>2026-10-13T08:09:08+00:00</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -14447,24 +14211,24 @@
       <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #رابین_بازار 🏛️ اختصاصی بازارگردانی رابین سهم 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۳ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۳۶:۵۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 14 views 08:09 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #بازرگام 🏛️ پست پیشگامان 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - انعقاد تفاهم نامه انحصاری لجستیک و ترخیص گمرکی- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۳۸:۳۶ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 20 views 08:09 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247663</t>
+          <t>https://t.me/codalboursetrader/247664</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>247664</t>
+          <t>247665</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T08:09:08+00:00</t>
+          <t>2026-10-13T08:15:08+00:00</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -14480,19 +14244,19 @@
       <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #بازرگام 🏛️ پست پیشگامان 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - انعقاد تفاهم نامه انحصاری لجستیک و ترخیص گمرکی- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۳۸:۳۶ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 20 views 08:09 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #رابین_بازار 🏛️ اختصاصی بازارگردانی رابین سهم 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۳ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۴۲:۱۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 08:15 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247664</t>
+          <t>https://t.me/codalboursetrader/247665</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>247665</t>
+          <t>247666</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -14513,24 +14277,24 @@
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #رابین_بازار 🏛️ اختصاصی بازارگردانی رابین سهم 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۳ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۴۲:۱۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 08:15 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #دامون 🏛️ آسمان دامون 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۴۲:۱۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 16 views 08:15 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247665</t>
+          <t>https://t.me/codalboursetrader/247666</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>247666</t>
+          <t>247667</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T08:15:08+00:00</t>
+          <t>2026-10-13T08:21:18+00:00</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -14540,30 +14304,30 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #دامون 🏛️ آسمان دامون 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۴۲:۱۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 16 views 08:15 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سبد_ایرانیان 🏛️ سبد گردان سرمایه ایرانیان 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ (حسابرسی نشده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۴۹:۵۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 15 views 08:21 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247666</t>
+          <t>https://t.me/codalboursetrader/247667</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>247667</t>
+          <t>247668</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T08:21:18+00:00</t>
+          <t>2026-10-13T08:27:04+00:00</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -14573,30 +14337,30 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سبد_ایرانیان 🏛️ سبد گردان سرمایه ایرانیان 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ (حسابرسی نشده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۴۹:۵۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 15 views 08:21 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #بپاس 🏛️ بیمه پاسارگاد 📌 #آگهی_ثبت_تصمیمات_مجمع_عادی_سالیانه 📋 آگهی ثبت تصمیمات مجمع عمومی عادی بطور فوق العاده دوره ۱۲ ماهه منتهی به ۱۴۰۵/۱۲/۲۹(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۵۴:۲۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 08:27 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247667</t>
+          <t>https://t.me/codalboursetrader/247668</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>247668</t>
+          <t>247669</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T08:27:04+00:00</t>
+          <t>2026-10-13T08:33:04+00:00</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -14612,24 +14376,24 @@
       <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #بپاس 🏛️ بیمه پاسارگاد 📌 #آگهی_ثبت_تصمیمات_مجمع_عادی_سالیانه 📋 آگهی ثبت تصمیمات مجمع عمومی عادی بطور فوق العاده دوره ۱۲ ماهه منتهی به ۱۴۰۵/۱۲/۲۹(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۵۴:۲۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 08:27 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آشنا_ثابت 🏛️ صندوق سرمایه گذاری امین آشنا ایرانیان 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۷/۲۲ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۰۰:۳۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 08:33 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247668</t>
+          <t>https://t.me/codalboursetrader/247669</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>247669</t>
+          <t>247670</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T08:33:04+00:00</t>
+          <t>2026-10-13T08:51:04+00:00</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -14645,24 +14409,24 @@
       <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آشنا_ثابت 🏛️ صندوق سرمایه گذاری امین آشنا ایرانیان 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۷/۲۲ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۰۰:۳۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 08:33 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ثقزوی 🏛️ توسعه عمران و سازندگی ایرانیان نوآور 📌 #مشخصات_کمیته_حسابرسی_و_واحد_حسابرسی_داخلی 📋 مشخصات کمیته حسابرسی و واحد حسابرسی داخلی(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۱۹:۵۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 15 views 08:51 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247669</t>
+          <t>https://t.me/codalboursetrader/247670</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>247670</t>
+          <t>247671</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T08:51:04+00:00</t>
+          <t>2026-10-13T08:51:05+00:00</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -14678,24 +14442,24 @@
       <c r="E89" s="2" t="inlineStr"/>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ثقزوی 🏛️ توسعه عمران و سازندگی ایرانیان نوآور 📌 #مشخصات_کمیته_حسابرسی_و_واحد_حسابرسی_داخلی 📋 مشخصات کمیته حسابرسی و واحد حسابرسی داخلی(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۱۹:۵۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 15 views 08:51 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پاسارگاد_بخشی 🏛️ بخشی صنایع پاسارگاد 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۲۰:۳۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 15 views 08:51 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247670</t>
+          <t>https://t.me/codalboursetrader/247671</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>247671</t>
+          <t>247672</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T08:51:05+00:00</t>
+          <t>2026-10-13T08:57:05+00:00</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -14705,25 +14469,25 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پاسارگاد_بخشی 🏛️ بخشی صنایع پاسارگاد 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۲۰:۳۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 15 views 08:51 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #هلد_سینا 🏛️ مادر تخصصی مالی و سرمایه گذاری سینا 📌 #گزارش_فعالیت_ماهانه_دوره_۱_ماهه 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۲۴:۴۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 08:57 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247671</t>
+          <t>https://t.me/codalboursetrader/247672</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>247672</t>
+          <t>247673</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -14738,30 +14502,30 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #هلد_سینا 🏛️ مادر تخصصی مالی و سرمایه گذاری سینا 📌 #گزارش_فعالیت_ماهانه_دوره_۱_ماهه 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۲۴:۴۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 08:57 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ومعادن 🏛️ سرمایه گذاری توسعه معادن و فلزات 📌 #توزیع_گواهی_نامه_نقل_و_انتقال_و_سپرده_سهام 📋 توزیع گواهی نامه نقل و انتقال و سپرده سهام 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۲۶:۱۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 08:57 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247672</t>
+          <t>https://t.me/codalboursetrader/247673</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>247673</t>
+          <t>247674</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T08:57:05+00:00</t>
+          <t>2026-10-13T09:00:14+00:00</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -14777,24 +14541,24 @@
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ومعادن 🏛️ سرمایه گذاری توسعه معادن و فلزات 📌 #توزیع_گواهی_نامه_نقل_و_انتقال_و_سپرده_سهام 📋 توزیع گواهی نامه نقل و انتقال و سپرده سهام 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۲۶:۱۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 08:57 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #خصدرا 🏛️ صنعتی دریائی ایران 📌 #آگهی_دعوت_به_مجمع_عمومی_فوق_العاده 📋 آگهی دعوت به مجمع عمومی فوق العاده دوره ۱۲ ماهه منتهی به ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۲۷:۵۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 27 views 09:00 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247673</t>
+          <t>https://t.me/codalboursetrader/247674</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>247674</t>
+          <t>247675</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T09:00:14+00:00</t>
+          <t>2026-10-13T09:06:08+00:00</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -14810,24 +14574,24 @@
       <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #خصدرا 🏛️ صنعتی دریائی ایران 📌 #آگهی_دعوت_به_مجمع_عمومی_فوق_العاده 📋 آگهی دعوت به مجمع عمومی فوق العاده دوره ۱۲ ماهه منتهی به ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۲۷:۵۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 27 views 09:00 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ماهور 🏛️ در اوراق بهادار با درآمد ثابت ماهور 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۳ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۳۶:۰۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 09:06 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247674</t>
+          <t>https://t.me/codalboursetrader/247675</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>247675</t>
+          <t>247676</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T09:06:08+00:00</t>
+          <t>2026-10-13T09:12:06+00:00</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -14843,24 +14607,24 @@
       <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ماهور 🏛️ در اوراق بهادار با درآمد ثابت ماهور 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۳ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۳۶:۰۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 09:06 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ثقزوی 🏛️ توسعه عمران و سازندگی ایرانیان نوآور 📋 مشخصات کمیته ریسک(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۴۱:۳۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 23 views 09:12 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247675</t>
+          <t>https://t.me/codalboursetrader/247676</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>247676</t>
+          <t>247677</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T09:12:06+00:00</t>
+          <t>2026-10-13T09:15:04+00:00</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -14870,30 +14634,30 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ثقزوی 🏛️ توسعه عمران و سازندگی ایرانیان نوآور 📋 مشخصات کمیته ریسک(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۴۱:۳۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 23 views 09:12 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ذوب 🏛️ ذوب آهن اصفهان 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) (شرکت باشگاه فرهنگی ورزشی ذوب آهن اصفهان) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۴۳:۰۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 26 views 09:15 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247676</t>
+          <t>https://t.me/codalboursetrader/247677</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>247677</t>
+          <t>247678</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T09:15:04+00:00</t>
+          <t>2026-10-13T09:18:10+00:00</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -14903,25 +14667,25 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ذوب 🏛️ ذوب آهن اصفهان 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) (شرکت باشگاه فرهنگی ورزشی ذوب آهن اصفهان) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۴۳:۰۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 26 views 09:15 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آوا 🏛️ آوای معیار 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۳ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۴۵:۰۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 33 views 09:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247677</t>
+          <t>https://t.me/codalboursetrader/247678</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>247678</t>
+          <t>247679</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -14942,24 +14706,24 @@
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آوا 🏛️ آوای معیار 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۳ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۴۵:۰۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 33 views 09:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #غبهار 🏛️ کشت و صنعت بهاران گلبهار خراسان 📌 #معرفی /تغییر_در_ترکیب_اعضای_هیئت _مدیره 📋 معرفی /تغییر در ترکیب اعضای هیئت مدیره/مدیر عامل 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۴۷:۳۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 32 views 09:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247678</t>
+          <t>https://t.me/codalboursetrader/247679</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>247679</t>
+          <t>247680</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T09:18:10+00:00</t>
+          <t>2026-10-13T09:21:10+00:00</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -14975,24 +14739,24 @@
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #غبهار 🏛️ کشت و صنعت بهاران گلبهار خراسان 📌 #معرفی /تغییر_در_ترکیب_اعضای_هیئت _مدیره 📋 معرفی /تغییر در ترکیب اعضای هیئت مدیره/مدیر عامل 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۴۷:۳۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 32 views 09:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📋 امیدنامه پذیرش در فرابورس ایران(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۴۸:۵۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 29 views 09:21 📋 اطلاعیه</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247679</t>
+          <t>https://t.me/codalboursetrader/247680</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>247680</t>
+          <t>247681</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T09:21:10+00:00</t>
+          <t>2026-10-13T09:21:11+00:00</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -15008,24 +14772,24 @@
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📋 امیدنامه پذیرش در فرابورس ایران(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۴۸:۵۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 29 views 09:21 📋 اطلاعیه</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #اهرم 🏛️ سهامی اهرمی کاریزما 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۳ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۵۰:۲۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 32 views 09:21 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247680</t>
+          <t>https://t.me/codalboursetrader/247681</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>247681</t>
+          <t>247682</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T09:21:11+00:00</t>
+          <t>2026-10-13T09:27:05+00:00</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -15041,24 +14805,24 @@
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #اهرم 🏛️ سهامی اهرمی کاریزما 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۳ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۵۰:۲۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 32 views 09:21 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #اهرم 🏛️ سهامی اهرمی کاریزما 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۳ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۵۶:۴۶ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 33 views 09:27 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247681</t>
+          <t>https://t.me/codalboursetrader/247682</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>247682</t>
+          <t>247683</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T09:27:05+00:00</t>
+          <t>2026-10-13T09:39:05+00:00</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -15074,24 +14838,24 @@
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #اهرم 🏛️ سهامی اهرمی کاریزما 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۳ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۲:۵۶:۴۶ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 33 views 09:27 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ره_آورد_ثابت 🏛️ ره آورد آباد مسکن 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۷/۲۲ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۳:۰۸:۴۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 28 views 09:39 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247682</t>
+          <t>https://t.me/codalboursetrader/247683</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>247642</t>
+          <t>247643</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T06:33:08+00:00</t>
+          <t>2026-10-13T06:39:06+00:00</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -15107,24 +14871,24 @@
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آواک 🏛️ صنایع ارتباطی آوا 📋 مشخصات کمیته ریسک(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۰:۰۰:۳۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 24 views 06:33 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #وشمال 🏛️ سرمایه گذاری چشم انداز توسعه شمال 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 توضیحات در خصوص اطلاعات و صورت های مالی منتشر شده 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۰:۰۶:۰۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 27 views 06:39 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247642</t>
+          <t>https://t.me/codalboursetrader/247643</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>247643</t>
+          <t>247644</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T06:39:06+00:00</t>
+          <t>2026-10-13T06:39:09+00:00</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -15140,24 +14904,24 @@
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #وشمال 🏛️ سرمایه گذاری چشم انداز توسعه شمال 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 توضیحات در خصوص اطلاعات و صورت های مالی منتشر شده 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۰:۰۶:۰۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 27 views 06:39 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #بهمن 🏛️ بهمن موتور 📌 #اظهارنظر_حسابرس_و_بازرس_قانونی_نسبت_به_گزارش_توجیهی_هیئت_مدیره_در_خصوص_افزایش_سرمایه 📋 اظهارنظر حسابرس و بازرس قانونی نسبت به گزارش توجیهی هیئت مدیره در خصوص افزایش سرمایه 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۰:۰۶:۴۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 25 views 06:39 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247643</t>
+          <t>https://t.me/codalboursetrader/247644</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>247644</t>
+          <t>247645</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T06:39:09+00:00</t>
+          <t>2026-10-13T06:48:05+00:00</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -15173,24 +14937,24 @@
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #بهمن 🏛️ بهمن موتور 📌 #اظهارنظر_حسابرس_و_بازرس_قانونی_نسبت_به_گزارش_توجیهی_هیئت_مدیره_در_خصوص_افزایش_سرمایه 📋 اظهارنظر حسابرس و بازرس قانونی نسبت به گزارش توجیهی هیئت مدیره در خصوص افزایش سرمایه 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۰:۰۶:۴۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 25 views 06:39 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شستان 🏛️ صنایع پتروشیمی شهید رئیسی گلستان 📌 #آگهی_ثبت_تصمیمات_مجمع_عادی_سالیانه 📋 آگهی ثبت تصمیمات مجمع عمومی فوق العاده (بجز تغییرات سرمایه) دوره ۱۲ ماهه منتهی به ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۰:۱۵:۴۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 24 views 06:48 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247644</t>
+          <t>https://t.me/codalboursetrader/247645</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>247645</t>
+          <t>247646</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T06:48:05+00:00</t>
+          <t>2026-10-13T06:48:06+00:00</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -15206,24 +14970,24 @@
       <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شستان 🏛️ صنایع پتروشیمی شهید رئیسی گلستان 📌 #آگهی_ثبت_تصمیمات_مجمع_عادی_سالیانه 📋 آگهی ثبت تصمیمات مجمع عمومی فوق العاده (بجز تغییرات سرمایه) دوره ۱۲ ماهه منتهی به ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۰:۱۵:۴۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 24 views 06:48 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پناه 🏛️ بخشی شایسته فردا 📋 صورت وضعیت پورتفوی صندوق سرمایه گذاری دوره ۱ ماهه منتهی به ۱۴۰۴/۰۷/۱۵ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۰:۱۶:۴۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 21 views 06:48 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247645</t>
+          <t>https://t.me/codalboursetrader/247646</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>247646</t>
+          <t>247647</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T06:48:06+00:00</t>
+          <t>2026-10-13T07:09:11+00:00</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -15239,24 +15003,24 @@
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پناه 🏛️ بخشی شایسته فردا 📋 صورت وضعیت پورتفوی صندوق سرمایه گذاری دوره ۱ ماهه منتهی به ۱۴۰۴/۰۷/۱۵ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۰:۱۶:۴۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 21 views 06:48 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیشرفت 🏛️ جسورانه پیشرفت 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۶ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۰:۳۷:۲۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 07:09 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247646</t>
+          <t>https://t.me/codalboursetrader/247647</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>247647</t>
+          <t>247648</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T07:09:11+00:00</t>
+          <t>2026-10-13T07:15:04+00:00</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -15272,24 +15036,24 @@
       <c r="E107" s="2" t="inlineStr"/>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیشرفت 🏛️ جسورانه پیشرفت 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۶ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۰:۳۷:۲۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 07:09 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #نیلپر 🏛️ تولیدی بازرگانی نیلپر 📌 #آگهی_دعوت_به_مجمع_عمومی_فوق_العاده 📋 آگهی دعوت به مجمع عمومی فوق العاده دوره ۱۲ ماهه منتهی به ۱۴۰۴/۱۲/۲۹(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۰:۴۲:۱۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 20 views 07:15 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247647</t>
+          <t>https://t.me/codalboursetrader/247648</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>247648</t>
+          <t>247649</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T07:15:04+00:00</t>
+          <t>2026-10-13T07:15:05+00:00</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -15305,24 +15069,24 @@
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #نیلپر 🏛️ تولیدی بازرگانی نیلپر 📌 #آگهی_دعوت_به_مجمع_عمومی_فوق_العاده 📋 آگهی دعوت به مجمع عمومی فوق العاده دوره ۱۲ ماهه منتهی به ۱۴۰۴/۱۲/۲۹(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۰:۴۲:۱۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 20 views 07:15 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #نیلپر 🏛️ تولیدی بازرگانی نیلپر 📌 #آگهی_دعوت_به_مجمع_عمومی_عادی_بطور_فوق_العاده 📋 آگهی دعوت به مجمع عمومی عادی بطور فوق العاده(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۰:۴۴:۵۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 07:15 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247648</t>
+          <t>https://t.me/codalboursetrader/247649</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>247649</t>
+          <t>247650</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T07:15:05+00:00</t>
+          <t>2026-10-13T07:18:06+00:00</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -15338,24 +15102,24 @@
       <c r="E109" s="2" t="inlineStr"/>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #نیلپر 🏛️ تولیدی بازرگانی نیلپر 📌 #آگهی_دعوت_به_مجمع_عمومی_عادی_بطور_فوق_العاده 📋 آگهی دعوت به مجمع عمومی عادی بطور فوق العاده(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۰:۴۴:۵۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 07:15 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #زشگزا 🏛️ شیر و گوشت زاگرس شهرکرد 📌 #معرفی /تغییر_در_ترکیب_اعضای_هیئت _مدیره 📋 معرفی /تغییر در ترکیب اعضای هیئت مدیره/مدیر عامل 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۰:۴۵:۲۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 19 views 07:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247649</t>
+          <t>https://t.me/codalboursetrader/247650</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>247650</t>
+          <t>247651</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T07:18:06+00:00</t>
+          <t>2026-10-13T07:18:07+00:00</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -15371,24 +15135,24 @@
       <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #زشگزا 🏛️ شیر و گوشت زاگرس شهرکرد 📌 #معرفی /تغییر_در_ترکیب_اعضای_هیئت _مدیره 📋 معرفی /تغییر در ترکیب اعضای هیئت مدیره/مدیر عامل 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۰:۴۵:۲۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 19 views 07:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #فافزا 🏛️ فولاد افزا سپاهان 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - صورتجلسه کار شات دان واحد گندله سازی فولاد مبارکه- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۰:۴۷:۳۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 07:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247650</t>
+          <t>https://t.me/codalboursetrader/247651</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>247651</t>
+          <t>247652</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T07:18:07+00:00</t>
+          <t>2026-10-13T07:24:09+00:00</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -15404,24 +15168,24 @@
       <c r="E111" s="2" t="inlineStr"/>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #فافزا 🏛️ فولاد افزا سپاهان 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - صورتجلسه کار شات دان واحد گندله سازی فولاد مبارکه- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۰:۴۷:۳۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 07:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #حکمت_بازار 🏛️ صندوق بازارگردانی حکمت ایرانیان یکم 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۷/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۰:۵۱:۴۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 07:24 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247651</t>
+          <t>https://t.me/codalboursetrader/247652</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>247652</t>
+          <t>247653</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T07:24:09+00:00</t>
+          <t>2026-10-13T07:36:03+00:00</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -15437,24 +15201,24 @@
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #حکمت_بازار 🏛️ صندوق بازارگردانی حکمت ایرانیان یکم 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۷/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۰:۵۱:۴۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 07:24 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شفا 🏛️ سرمایه گذاری شفادارو 📌 #اطلاعات_حاصل_از_برگزاری_کنفرانس_اطلاع_رسانی 📋 اطلاعات حاصل از برگزاری کنفرانس اطلاع رسانی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۰۳:۰۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 14 views 07:36 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247652</t>
+          <t>https://t.me/codalboursetrader/247653</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>247653</t>
+          <t>247654</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T07:36:03+00:00</t>
+          <t>2026-10-13T07:39:06+00:00</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -15470,24 +15234,24 @@
       <c r="E113" s="2" t="inlineStr"/>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شفا 🏛️ سرمایه گذاری شفادارو 📌 #اطلاعات_حاصل_از_برگزاری_کنفرانس_اطلاع_رسانی 📋 اطلاعات حاصل از برگزاری کنفرانس اطلاع رسانی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۰۳:۰۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 14 views 07:36 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ثقزوی 🏛️ توسعه عمران و سازندگی ایرانیان نوآور 📋 مشخصات کمیته ریسک 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۰۸:۴۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 19 views 07:39 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247653</t>
+          <t>https://t.me/codalboursetrader/247654</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>247654</t>
+          <t>247655</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T07:39:06+00:00</t>
+          <t>2026-10-13T07:42:07+00:00</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -15503,24 +15267,24 @@
       <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ثقزوی 🏛️ توسعه عمران و سازندگی ایرانیان نوآور 📋 مشخصات کمیته ریسک 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۰۸:۴۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 19 views 07:39 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آرمان_اندیش_بازار 🏛️ صندوق اختصاصی بازارگردانی آرمان اندیش 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۷/۲۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۰۹:۱۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 19 views 07:42 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247654</t>
+          <t>https://t.me/codalboursetrader/247655</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>247655</t>
+          <t>247656</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T07:42:07+00:00</t>
+          <t>2026-10-13T07:54:03+00:00</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -15536,24 +15300,24 @@
       <c r="E115" s="2" t="inlineStr"/>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آرمان_اندیش_بازار 🏛️ صندوق اختصاصی بازارگردانی آرمان اندیش 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۷/۲۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۰۹:۱۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 19 views 07:42 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ضمان 🏛️ تضمین اصل سرمایه کاریزما 📋 تصمیمات مجمع صندوق سرمایه گذاری(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۲۱:۵۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 20 views 07:54 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247655</t>
+          <t>https://t.me/codalboursetrader/247656</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>247656</t>
+          <t>247657</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T07:54:03+00:00</t>
+          <t>2026-10-13T07:54:04+00:00</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -15569,24 +15333,24 @@
       <c r="E116" s="2" t="inlineStr"/>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ضمان 🏛️ تضمین اصل سرمایه کاریزما 📋 تصمیمات مجمع صندوق سرمایه گذاری(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۲۱:۵۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 20 views 07:54 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تاصیکو 🏛️ سرمایه گذاری صدر تامین 📌 #اطلاعات_حاصل_از_برگزاری_کنفرانس_اطلاع_رسانی 📋 اطلاعات حاصل از برگزاری کنفرانس اطلاع رسانی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۲۲:۴۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 24 views 07:54 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247656</t>
+          <t>https://t.me/codalboursetrader/247657</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>247657</t>
+          <t>247658</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T07:54:04+00:00</t>
+          <t>2026-10-13T07:54:05+00:00</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -15602,24 +15366,24 @@
       <c r="E117" s="2" t="inlineStr"/>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تاصیکو 🏛️ سرمایه گذاری صدر تامین 📌 #اطلاعات_حاصل_از_برگزاری_کنفرانس_اطلاع_رسانی 📋 اطلاعات حاصل از برگزاری کنفرانس اطلاع رسانی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۲۲:۴۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 24 views 07:54 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کخاک 🏛️ صنایع خاک چینی ایران 📋 عدم پاسخگویی ناشر در خصوص لزوم برگزاری کنفرانس اطلاع رسانی و افشای اهم مطالب مطرح شده 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۲۳:۱۶ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 07:54 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247657</t>
+          <t>https://t.me/codalboursetrader/247658</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>247658</t>
+          <t>247659</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T07:54:05+00:00</t>
+          <t>2026-10-13T07:57:04+00:00</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -15635,24 +15399,24 @@
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کخاک 🏛️ صنایع خاک چینی ایران 📋 عدم پاسخگویی ناشر در خصوص لزوم برگزاری کنفرانس اطلاع رسانی و افشای اهم مطالب مطرح شده 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۲۳:۱۶ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 07:54 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #رویان_نیکو 🏛️ صندوق سرمایه گذاری نیکوکاری لوتوس رویان 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۲ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۲۴:۴۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 16 views 07:57 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247658</t>
+          <t>https://t.me/codalboursetrader/247659</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>247659</t>
+          <t>247660</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T07:57:04+00:00</t>
+          <t>2026-10-13T07:57:05+00:00</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -15668,24 +15432,24 @@
       <c r="E119" s="2" t="inlineStr"/>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #رویان_نیکو 🏛️ صندوق سرمایه گذاری نیکوکاری لوتوس رویان 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۲ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۲۴:۴۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 16 views 07:57 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ضمان 🏛️ تضمین اصل سرمایه کاریزما 📋 تصمیمات مجمع صندوق سرمایه گذاری(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۲۵:۴۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 15 views 07:57 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247659</t>
+          <t>https://t.me/codalboursetrader/247660</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>247660</t>
+          <t>247661</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T07:57:05+00:00</t>
+          <t>2026-10-13T08:00:11+00:00</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -15701,24 +15465,24 @@
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ضمان 🏛️ تضمین اصل سرمایه کاریزما 📋 تصمیمات مجمع صندوق سرمایه گذاری(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۲۵:۴۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 15 views 07:57 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #رویان_نیکو 🏛️ صندوق سرمایه گذاری نیکوکاری لوتوس رویان 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۲ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۲۷:۳۶ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 14 views 08:00 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247660</t>
+          <t>https://t.me/codalboursetrader/247661</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>247661</t>
+          <t>247662</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T08:00:11+00:00</t>
+          <t>2026-10-13T08:00:13+00:00</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -15728,30 +15492,30 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #رویان_نیکو 🏛️ صندوق سرمایه گذاری نیکوکاری لوتوس رویان 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۸/۰۲ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۲۷:۳۶ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 14 views 08:00 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کسعدی 🏛️ کارخانجات کاشی و سرامیک سعدی 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۱:۲۷:۴۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 16 views 08:00 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247661</t>
+          <t>https://t.me/codalboursetrader/247662</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>247621</t>
+          <t>247622</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T05:27:06+00:00</t>
+          <t>2026-10-13T05:27:08+00:00</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -15767,24 +15531,24 @@
       <c r="E122" s="2" t="inlineStr"/>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ولشرق 🏛️ لیزینگ ایران و شرق 📋 توقف نماد معاملاتی ناشر به استناد ماده ۱۹ مکرر/ ۱۲ مکرر ۳دستورالعمل اجرایی نحوه انجام معاملات 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۵۵:۴۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 23 views 05:27 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #غپاذر 🏛️ شیر پاستوریزه پگاه آذربایجان شرقی 📌 #مشخصات_کمیته_حسابرسی_و_واحد_حسابرسی_داخلی 📋 مشخصات کمیته حسابرسی و واحد حسابرسی داخلی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۵۶:۳۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 20 views 05:27 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247621</t>
+          <t>https://t.me/codalboursetrader/247622</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>247622</t>
+          <t>247623</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T05:27:08+00:00</t>
+          <t>2026-10-13T05:30:04+00:00</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -15800,24 +15564,24 @@
       <c r="E123" s="2" t="inlineStr"/>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #غپاذر 🏛️ شیر پاستوریزه پگاه آذربایجان شرقی 📌 #مشخصات_کمیته_حسابرسی_و_واحد_حسابرسی_داخلی 📋 مشخصات کمیته حسابرسی و واحد حسابرسی داخلی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۵۶:۳۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 20 views 05:27 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شفن 🏛️ پتروشیمی فن آوران 📌 #مشخصات_کمیته_حسابرسی_و_واحد_حسابرسی_داخلی 📋 مشخصات کمیته حسابرسی و واحد حسابرسی داخلی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۵۷:۱۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 19 views 05:30 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247622</t>
+          <t>https://t.me/codalboursetrader/247623</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>247623</t>
+          <t>247624</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T05:30:04+00:00</t>
+          <t>2026-10-13T05:33:05+00:00</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -15833,24 +15597,24 @@
       <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شفن 🏛️ پتروشیمی فن آوران 📌 #مشخصات_کمیته_حسابرسی_و_واحد_حسابرسی_داخلی 📋 مشخصات کمیته حسابرسی و واحد حسابرسی داخلی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۵۷:۱۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 19 views 05:30 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شراز 🏛️ پالایش نفت شیراز 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - ابلاغیه دستورالعمل قیمت گذاری نفت خام و فرآورده ها- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۰۲:۰۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 19 views 05:33 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247623</t>
+          <t>https://t.me/codalboursetrader/247624</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>247624</t>
+          <t>247625</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T05:33:05+00:00</t>
+          <t>2026-10-13T05:39:07+00:00</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -15866,24 +15630,24 @@
       <c r="E125" s="2" t="inlineStr"/>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شراز 🏛️ پالایش نفت شیراز 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - ابلاغیه دستورالعمل قیمت گذاری نفت خام و فرآورده ها- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۰۲:۰۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 19 views 05:33 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #چخزر 🏛️ صنایع چوب خزر کاسپین 📌 #اطلاعات_حاصل_از_برگزاری_کنفرانس_اطلاع_رسانی 📋 اطلاعات حاصل از برگزاری کنفرانس اطلاع رسانی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۰۷:۲۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 21 views 05:39 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247624</t>
+          <t>https://t.me/codalboursetrader/247625</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>247625</t>
+          <t>247626</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T05:39:07+00:00</t>
+          <t>2026-10-13T05:48:04+00:00</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -15899,24 +15663,24 @@
       <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #چخزر 🏛️ صنایع چوب خزر کاسپین 📌 #اطلاعات_حاصل_از_برگزاری_کنفرانس_اطلاع_رسانی 📋 اطلاعات حاصل از برگزاری کنفرانس اطلاع رسانی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۰۷:۲۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 21 views 05:39 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شبریز 🏛️ پالایش نفت تبریز 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - تصویب نامه هیات وزیران در خصوص قیمت گذاری خوراک- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۱۵:۴۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 26 views 05:48 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247625</t>
+          <t>https://t.me/codalboursetrader/247626</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>247626</t>
+          <t>247627</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T05:48:04+00:00</t>
+          <t>2026-10-13T05:51:08+00:00</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -15932,24 +15696,24 @@
       <c r="E127" s="2" t="inlineStr"/>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شبریز 🏛️ پالایش نفت تبریز 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - تصویب نامه هیات وزیران در خصوص قیمت گذاری خوراک- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۱۵:۴۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 26 views 05:48 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کوچین 🏛️ تولیدی کوچین 📌 #آگهی_دعوت_به_مجمع_عمومی_عادی_بطور_فوق_العاده 📋 آگهی دعوت به مجمع عمومی عادی بطور فوق العاده 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۱۸:۲۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 24 views 05:51 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247626</t>
+          <t>https://t.me/codalboursetrader/247627</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>247627</t>
+          <t>247628</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T05:51:08+00:00</t>
+          <t>2026-10-13T05:51:09+00:00</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -15965,24 +15729,24 @@
       <c r="E128" s="2" t="inlineStr"/>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کوچین 🏛️ تولیدی کوچین 📌 #آگهی_دعوت_به_مجمع_عمومی_عادی_بطور_فوق_العاده 📋 آگهی دعوت به مجمع عمومی عادی بطور فوق العاده 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۱۸:۲۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 24 views 05:51 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شپنا 🏛️ پالایش نفت اصفهان 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - تصویب نامه هیئت وزیران قیمت خوراک و فراورده- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۲۰:۰۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 25 views 05:51 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247627</t>
+          <t>https://t.me/codalboursetrader/247628</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>247628</t>
+          <t>247629</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T05:51:09+00:00</t>
+          <t>2026-10-13T05:57:04+00:00</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -15998,24 +15762,24 @@
       <c r="E129" s="2" t="inlineStr"/>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شپنا 🏛️ پالایش نفت اصفهان 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - تصویب نامه هیئت وزیران قیمت خوراک و فراورده- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۲۰:۰۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 25 views 05:51 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #مهرگان 🏛️ گروه مالی مهرگان تامین پارس 📌 #زمان_بندی_پرداخت_سود 📋 زمانبندی پرداخت سود دوره ۱۲ ماهه منتهی به ۱۴۰۴/۱۲/۲۹(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۲۴:۱۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 20 views 05:57 📋 اطلاعیه</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247628</t>
+          <t>https://t.me/codalboursetrader/247629</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>247629</t>
+          <t>247630</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T05:57:04+00:00</t>
+          <t>2026-10-13T06:00:16+00:00</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -16031,24 +15795,24 @@
       <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #مهرگان 🏛️ گروه مالی مهرگان تامین پارس 📌 #زمان_بندی_پرداخت_سود 📋 زمانبندی پرداخت سود دوره ۱۲ ماهه منتهی به ۱۴۰۴/۱۲/۲۹(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۲۴:۱۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 20 views 05:57 📋 اطلاعیه</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #حپترو 🏛️ مهندسی حمل و نقل پتروشیمی 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (تغییر در مفاد هر نوع اطلاعیه بااهمیتی که قبلاً منتشر شده است - گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۲۹:۳۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 15 views 06:00 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247629</t>
+          <t>https://t.me/codalboursetrader/247630</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>247630</t>
+          <t>247631</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T06:00:16+00:00</t>
+          <t>2026-10-13T06:12:05+00:00</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -16058,30 +15822,30 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr"/>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #حپترو 🏛️ مهندسی حمل و نقل پتروشیمی 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (تغییر در مفاد هر نوع اطلاعیه بااهمیتی که قبلاً منتشر شده است - گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۲۹:۳۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 15 views 06:00 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #وتکادو 🏛️ سرمایه گذاری آتیه تکادو 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ (حسابرسی نشده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۴۰:۲۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 06:12 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247630</t>
+          <t>https://t.me/codalboursetrader/247631</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>247631</t>
+          <t>247632</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T06:12:05+00:00</t>
+          <t>2026-10-13T06:15:06+00:00</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -16097,24 +15861,24 @@
       <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #وتکادو 🏛️ سرمایه گذاری آتیه تکادو 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ (حسابرسی نشده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۴۰:۲۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 06:12 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #مدار 🏛️ سرمایه گذاری مدیریت سرمایه مدار 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۴۲:۴۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 06:15 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247631</t>
+          <t>https://t.me/codalboursetrader/247632</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>247632</t>
+          <t>247633</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T06:15:06+00:00</t>
+          <t>2026-10-13T06:15:07+00:00</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -16124,25 +15888,25 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr"/>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #مدار 🏛️ سرمایه گذاری مدیریت سرمایه مدار 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۴۲:۴۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 06:15 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #زماهان 🏛️ مجتمع تولید گوشت مرغ ماهان 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (افشای معاملات موضوع ماده ۱۲۹ اصلاحیه قانون تجارت، یا سایر اشخاص وابسته - گروه ب) منتهی به سال مالی ۱۴۰۵/۰۹/۳۰(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۴۳:۳۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 06:15 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247632</t>
+          <t>https://t.me/codalboursetrader/247633</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>247633</t>
+          <t>247634</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -16157,30 +15921,30 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #زماهان 🏛️ مجتمع تولید گوشت مرغ ماهان 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (افشای معاملات موضوع ماده ۱۲۹ اصلاحیه قانون تجارت، یا سایر اشخاص وابسته - گروه ب) منتهی به سال مالی ۱۴۰۵/۰۹/۳۰(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۴۳:۳۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 06:15 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سمگا 🏛️ گروه سرمایه گذاری میراث فرهنگی و گردشگری ایران 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) (شرکت پارس زیگورات سیرجان) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۴۴:۰۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 27 views 06:15 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247633</t>
+          <t>https://t.me/codalboursetrader/247634</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>247634</t>
+          <t>247635</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T06:15:07+00:00</t>
+          <t>2026-10-13T06:18:16+00:00</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -16190,30 +15954,30 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr"/>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سمگا 🏛️ گروه سرمایه گذاری میراث فرهنگی و گردشگری ایران 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) (شرکت پارس زیگورات سیرجان) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۴۴:۰۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 27 views 06:15 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کرمان 🏛️ سرمایه گذاری توسعه و عمران استان کرمان 📌 #گزارش_فعالیت_هیئت_مدیره 📋 گزارش فعالیت هیئت مدیره دوره ۱۲ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۴۶:۴۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 25 views 06:18 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247634</t>
+          <t>https://t.me/codalboursetrader/247635</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>247635</t>
+          <t>247636</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T06:18:16+00:00</t>
+          <t>2026-10-13T06:18:17+00:00</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -16223,30 +15987,30 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کرمان 🏛️ سرمایه گذاری توسعه و عمران استان کرمان 📌 #گزارش_فعالیت_هیئت_مدیره 📋 گزارش فعالیت هیئت مدیره دوره ۱۲ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۴۶:۴۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 25 views 06:18 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سمگا 🏛️ گروه سرمایه گذاری میراث فرهنگی و گردشگری ایران 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) (شرکت آروین زیگورات عمران) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۴۷:۱۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 20 views 06:18 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247635</t>
+          <t>https://t.me/codalboursetrader/247636</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>247636</t>
+          <t>247637</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T06:18:17+00:00</t>
+          <t>2026-10-13T06:21:10+00:00</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -16262,24 +16026,24 @@
       <c r="E137" s="2" t="inlineStr"/>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سمگا 🏛️ گروه سرمایه گذاری میراث فرهنگی و گردشگری ایران 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) (شرکت آروین زیگورات عمران) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۴۷:۱۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 20 views 06:18 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سمگا 🏛️ گروه سرمایه گذاری میراث فرهنگی و گردشگری ایران 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) (شرکت توسعه مجتمع های خدماتی رفاهی پارس زیگورات) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۴۸:۵۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 15 views 06:21 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247636</t>
+          <t>https://t.me/codalboursetrader/247637</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>247637</t>
+          <t>247638</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T06:21:10+00:00</t>
+          <t>2026-10-13T06:24:03+00:00</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -16295,24 +16059,24 @@
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سمگا 🏛️ گروه سرمایه گذاری میراث فرهنگی و گردشگری ایران 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) (شرکت توسعه مجتمع های خدماتی رفاهی پارس زیگورات) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۴۸:۵۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 15 views 06:21 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #وسپهر_اعتماد_آفرین 🏛️ سرمایه گذاری سپهر اعتماد آفرین 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۵۱:۴۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 06:24 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247637</t>
+          <t>https://t.me/codalboursetrader/247638</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>247638</t>
+          <t>247639</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T06:24:03+00:00</t>
+          <t>2026-10-13T06:24:04+00:00</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -16322,30 +16086,30 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr"/>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #وسپهر_اعتماد_آفرین 🏛️ سرمایه گذاری سپهر اعتماد آفرین 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۵۱:۴۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 18 views 06:24 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شفن 🏛️ پتروشیمی فن آوران 📋 مشخصات کمیته ریسک 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۵۲:۴۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 16 views 06:24 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247638</t>
+          <t>https://t.me/codalboursetrader/247639</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>247639</t>
+          <t>247640</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T06:24:04+00:00</t>
+          <t>2026-10-13T06:27:03+00:00</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -16361,24 +16125,24 @@
       <c r="E140" s="2" t="inlineStr"/>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شفن 🏛️ پتروشیمی فن آوران 📋 مشخصات کمیته ریسک 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۵۲:۴۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 16 views 06:24 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #نیکی_بازار 🏛️ اختصاصی بازارگردانی توسعه سهام نیکی 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۷/۲۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۵۴:۰۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 20 views 06:27 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247639</t>
+          <t>https://t.me/codalboursetrader/247640</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>247640</t>
+          <t>247641</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T06:27:03+00:00</t>
+          <t>2026-10-13T06:27:04+00:00</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -16394,24 +16158,24 @@
       <c r="E141" s="2" t="inlineStr"/>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #نیکی_بازار 🏛️ اختصاصی بازارگردانی توسعه سهام نیکی 📋 آگهی دعوت به مجمع صندوق سرمایه گذاری در تاریخ ۱۴۰۵/۰۷/۲۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۵۴:۰۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 20 views 06:27 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #غنیلی 🏛️ مجتمع تولیدی نیلی صنعت کرمان 📌 #آگهی_دعوت_به_مجمع_عمومی_عادی_بطور_فوق_العاده 📋 آگهی دعوت به مجمع عمومی عادی بطور فوق العاده 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۹:۵۵:۴۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 06:27 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247640</t>
+          <t>https://t.me/codalboursetrader/247641</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>247600</t>
+          <t>247601</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:39:04+00:00</t>
+          <t>2026-10-12T15:42:05+00:00</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -16427,24 +16191,24 @@
       <c r="E142" s="2" t="inlineStr"/>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تادیکو 🏛️ گروه سرمایه گذاری کشت و دام و صنایع لبنی تامین 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - نتیجه نهایی دعوی له شرکت- گروه ب) منتهی به سال مالی ۱۴۰۶/۰۲/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۰۷:۴۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 38 views 15:39 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #زماهان 🏛️ مجتمع تولید گوشت مرغ ماهان 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (افشای معاملات موضوع ماده ۱۲۹ اصلاحیه قانون تجارت، یا سایر اشخاص وابسته - گروه ب) منتهی به سال مالی ۱۴۰۵/۰۹/۳۰(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۱۱:۳۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 39 views 15:42 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247600</t>
+          <t>https://t.me/codalboursetrader/247601</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>247601</t>
+          <t>247602</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:42:05+00:00</t>
+          <t>2026-10-12T15:48:04+00:00</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -16460,24 +16224,24 @@
       <c r="E143" s="2" t="inlineStr"/>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #زماهان 🏛️ مجتمع تولید گوشت مرغ ماهان 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (افشای معاملات موضوع ماده ۱۲۹ اصلاحیه قانون تجارت، یا سایر اشخاص وابسته - گروه ب) منتهی به سال مالی ۱۴۰۵/۰۹/۳۰(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۱۱:۳۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 38 views 15:42 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پرسپولیس 🏛️ فرهنگی ورزشی پرسپولیس 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - خرید تیم نونهالان- گروه ب) منتهی به سال مالی ۱۴۰۶/۰۳/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۱۵:۴۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 30 views 15:48 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247601</t>
+          <t>https://t.me/codalboursetrader/247602</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>247602</t>
+          <t>247603</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:48:04+00:00</t>
+          <t>2026-10-12T15:51:04+00:00</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -16493,24 +16257,24 @@
       <c r="E144" s="2" t="inlineStr"/>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پرسپولیس 🏛️ فرهنگی ورزشی پرسپولیس 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - خرید تیم نونهالان- گروه ب) منتهی به سال مالی ۱۴۰۶/۰۳/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۱۵:۴۹ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 29 views 15:48 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #فنورد 🏛️ نورد و تولید قطعات فولادی 📌 #لغو_آگهی_ (اطلاعیه)_دعوت_به_مجمع_عمومی 📋 لغو آگهی (اطلاعیه) دعوت به مجمع عمومی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۱۸:۳۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 15:51 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247602</t>
+          <t>https://t.me/codalboursetrader/247603</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>247603</t>
+          <t>247604</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:51:04+00:00</t>
+          <t>2026-10-12T15:51:05+00:00</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -16526,24 +16290,24 @@
       <c r="E145" s="2" t="inlineStr"/>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #فنورد 🏛️ نورد و تولید قطعات فولادی 📌 #لغو_آگهی_ (اطلاعیه)_دعوت_به_مجمع_عمومی 📋 لغو آگهی (اطلاعیه) دعوت به مجمع عمومی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۱۸:۳۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 15:51 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #فنورد 🏛️ نورد و تولید قطعات فولادی 📌 #آگهی_دعوت_به_مجمع_عمومی_عادی_بطور_فوق_العاده 📋 آگهی دعوت به مجمع عمومی عادی بطور فوق العاده 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۱۹:۵۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 32 views 15:51 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247603</t>
+          <t>https://t.me/codalboursetrader/247604</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>247604</t>
+          <t>247605</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:51:05+00:00</t>
+          <t>2026-10-12T15:54:04+00:00</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -16559,24 +16323,24 @@
       <c r="E146" s="2" t="inlineStr"/>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #فنورد 🏛️ نورد و تولید قطعات فولادی 📌 #آگهی_دعوت_به_مجمع_عمومی_عادی_بطور_فوق_العاده 📋 آگهی دعوت به مجمع عمومی عادی بطور فوق العاده 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۱۹:۵۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 32 views 15:51 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پاسا 🏛️ ایران یاسا تایر و رابر 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - افزایش درنرخ فروش برخی ازمحصولات- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۲۱:۴۶ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 45 views 15:54 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247604</t>
+          <t>https://t.me/codalboursetrader/247605</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>247605</t>
+          <t>247606</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:54:04+00:00</t>
+          <t>2026-10-12T15:54:06+00:00</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -16586,30 +16350,30 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr"/>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پاسا 🏛️ ایران یاسا تایر و رابر 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - افزایش درنرخ فروش برخی ازمحصولات- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۲۱:۴۶ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 45 views 15:54 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سبد_تدبیر 🏛️ سبدگردان تدبیر 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۲۲:۱۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 54 views 15:54 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247605</t>
+          <t>https://t.me/codalboursetrader/247606</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>247606</t>
+          <t>247607</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T15:54:06+00:00</t>
+          <t>2026-10-12T16:15:17+00:00</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -16625,24 +16389,24 @@
       <c r="E148" s="2" t="inlineStr"/>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #سبد_تدبیر 🏛️ سبدگردان تدبیر 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۲۲:۱۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 53 views 15:54 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #طیور 🏛️ طیور دانه سلامت دزفول 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۳ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی نشده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۴۳:۵۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 60 views 16:15 📋 اطلاعیه 📕 PDF 📘 Excel</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247606</t>
+          <t>https://t.me/codalboursetrader/247607</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>247607</t>
+          <t>247608</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T16:15:17+00:00</t>
+          <t>2026-10-12T17:15:14+00:00</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -16658,24 +16422,24 @@
       <c r="E149" s="2" t="inlineStr"/>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #طیور 🏛️ طیور دانه سلامت دزفول 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۳ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی نشده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۱۹:۴۳:۵۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 59 views 16:15 📋 اطلاعیه 📕 PDF 📘 Excel</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #دتولید 🏛️ داروسازی تولید دارو 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۲۰:۴۵:۰۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 57 views 17:15 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247607</t>
+          <t>https://t.me/codalboursetrader/247608</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>247608</t>
+          <t>247609</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12T17:15:14+00:00</t>
+          <t>2026-10-13T04:18:09+00:00</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -16685,30 +16449,30 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr"/>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #دتولید 🏛️ داروسازی تولید دارو 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۰ ۲۰:۴۵:۰۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 56 views 17:15 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تشتاد 🏛️ صنایع تولیدی اشتاد ایران 📌 #آگهی_ثبت_تصمیمات_مجمع_عادی_سالیانه 📋 آگهی ثبت تصمیمات مجمع عمومی عادی بطور فوق العاده دوره ۱۲ ماهه منتهی به ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۷:۴۷:۰۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 34 views 04:18 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247608</t>
+          <t>https://t.me/codalboursetrader/247609</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>247609</t>
+          <t>247610</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T04:18:09+00:00</t>
+          <t>2026-10-13T04:27:05+00:00</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -16718,30 +16482,30 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr"/>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تشتاد 🏛️ صنایع تولیدی اشتاد ایران 📌 #آگهی_ثبت_تصمیمات_مجمع_عادی_سالیانه 📋 آگهی ثبت تصمیمات مجمع عمومی عادی بطور فوق العاده دوره ۱۲ ماهه منتهی به ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۷:۴۷:۰۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 33 views 04:18 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #درین 🏛️ درین آتا 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۳ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ (حسابرسی نشده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۷:۵۴:۱۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 32 views 04:27 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247609</t>
+          <t>https://t.me/codalboursetrader/247610</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>247610</t>
+          <t>247611</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T04:27:05+00:00</t>
+          <t>2026-10-13T04:39:06+00:00</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -16757,24 +16521,24 @@
       <c r="E152" s="2" t="inlineStr"/>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #درین 🏛️ درین آتا 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۳ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ (حسابرسی نشده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۷:۵۴:۱۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 32 views 04:27 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #فن_آوا 🏛️ گروه فن اوا 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) (شرکت تضمین گستر فن آوا) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۰۶:۴۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 26 views 04:39 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247610</t>
+          <t>https://t.me/codalboursetrader/247611</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>247611</t>
+          <t>247612</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T04:39:06+00:00</t>
+          <t>2026-10-13T04:42:06+00:00</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -16790,24 +16554,24 @@
       <c r="E153" s="2" t="inlineStr"/>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #فن_آوا 🏛️ گروه فن اوا 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۶ ماهه منتهی به ۱۴۰۵/۰۳/۳۱ (حسابرسی شده) (شرکت تضمین گستر فن آوا) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۰۶:۴۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 26 views 04:39 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #مروارید 🏛️ مروارید آتا 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۳ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ (حسابرسی نشده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۰۹:۰۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 04:42 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247611</t>
+          <t>https://t.me/codalboursetrader/247612</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>247612</t>
+          <t>247613</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T04:42:06+00:00</t>
+          <t>2026-10-13T04:48:06+00:00</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -16817,30 +16581,30 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #مروارید 🏛️ مروارید آتا 📌 #صورت_های_مالی_میان_دوره_ای 📋 اطلاعات و صورت های مالی میاندوره ای دوره ۳ ماهه منتهی به ۱۴۰۵/۰۶/۳۱ (حسابرسی نشده) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۰۹:۰۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 04:42 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شلیا 🏛️ مواد ویژه لیا 📋 کمیته انتصابات(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۱۷:۲۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 20 views 04:48 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247612</t>
+          <t>https://t.me/codalboursetrader/247613</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>247613</t>
+          <t>247614</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T04:48:06+00:00</t>
+          <t>2026-10-13T04:57:05+00:00</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -16856,24 +16620,24 @@
       <c r="E155" s="2" t="inlineStr"/>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شلیا 🏛️ مواد ویژه لیا 📋 کمیته انتصابات(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۱۷:۲۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 20 views 04:48 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شلیا 🏛️ مواد ویژه لیا 📌 #مشخصات_کمیته_حسابرسی_و_واحد_حسابرسی_داخلی 📋 مشخصات کمیته حسابرسی و واحد حسابرسی داخلی(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۲۶:۵۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 04:57 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247613</t>
+          <t>https://t.me/codalboursetrader/247614</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>247614</t>
+          <t>247615</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T04:57:05+00:00</t>
+          <t>2026-10-13T05:00:08+00:00</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -16889,24 +16653,24 @@
       <c r="E156" s="2" t="inlineStr"/>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شلیا 🏛️ مواد ویژه لیا 📌 #مشخصات_کمیته_حسابرسی_و_واحد_حسابرسی_داخلی 📋 مشخصات کمیته حسابرسی و واحد حسابرسی داخلی(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۲۶:۵۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 17 views 04:57 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شتران 🏛️ پالایش نفت تهران 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - تصویب نامه هیئت وزیران(قیمت گذاری خوراک و فرآورده)- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۲۷:۱۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 150 views 05:00 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247614</t>
+          <t>https://t.me/codalboursetrader/247615</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>247615</t>
+          <t>247616</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T05:00:08+00:00</t>
+          <t>2026-10-13T05:03:04+00:00</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -16922,24 +16686,24 @@
       <c r="E157" s="2" t="inlineStr"/>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شتران 🏛️ پالایش نفت تهران 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - تصویب نامه هیئت وزیران(قیمت گذاری خوراک و فرآورده)- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۲۷:۱۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 150 views 05:00 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شاوان 🏛️ پالایش نفت لاوان 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - ابلاغیه دستورالعمل قیمت گذاری نفت خام و فرآورده- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۳۲:۴۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 05:03 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247615</t>
+          <t>https://t.me/codalboursetrader/247616</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>247616</t>
+          <t>247617</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T05:03:04+00:00</t>
+          <t>2026-10-13T05:06:05+00:00</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -16955,24 +16719,24 @@
       <c r="E158" s="2" t="inlineStr"/>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شاوان 🏛️ پالایش نفت لاوان 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (سایر اطلاعات بااهمیت - ابلاغیه دستورالعمل قیمت گذاری نفت خام و فرآورده- گروه ب) منتهی به سال مالی ۱۴۰۵/۱۲/۲۹ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۳۲:۴۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 05:03 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #غدشت 🏛️ فرآورده های غذایی دشت مرغاب 📌 #آگهی_ثبت_افزایش_سرمایه 📋 آگهی ثبت افزایش سرمایه(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۳۵:۱۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 21 views 05:06 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247616</t>
+          <t>https://t.me/codalboursetrader/247617</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>247617</t>
+          <t>247618</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T05:06:05+00:00</t>
+          <t>2026-10-13T05:15:04+00:00</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -16988,24 +16752,24 @@
       <c r="E159" s="2" t="inlineStr"/>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #غدشت 🏛️ فرآورده های غذایی دشت مرغاب 📌 #آگهی_ثبت_افزایش_سرمایه 📋 آگهی ثبت افزایش سرمایه(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۳۵:۱۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 21 views 05:06 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #رایا 🏛️ بیمه اتکایی رایا 📌 #مشخصات_کمیته_حسابرسی_و_واحد_حسابرسی_داخلی 📋 مشخصات کمیته حسابرسی و واحد حسابرسی داخلی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۴۳:۳۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 05:15 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247617</t>
+          <t>https://t.me/codalboursetrader/247618</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>247618</t>
+          <t>247619</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T05:15:04+00:00</t>
+          <t>2026-10-13T05:24:04+00:00</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -17021,24 +16785,24 @@
       <c r="E160" s="2" t="inlineStr"/>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #رایا 🏛️ بیمه اتکایی رایا 📌 #مشخصات_کمیته_حسابرسی_و_واحد_حسابرسی_داخلی 📋 مشخصات کمیته حسابرسی و واحد حسابرسی داخلی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۴۳:۳۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 22 views 05:15 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #رایا 🏛️ بیمه اتکایی رایا 📋 مشخصات کمیته ریسک 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۵۳:۳۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 23 views 05:24 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247618</t>
+          <t>https://t.me/codalboursetrader/247619</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>247619</t>
+          <t>247620</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T05:24:04+00:00</t>
+          <t>2026-10-13T05:27:06+00:00</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -17048,18 +16812,18 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr"/>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #رایا 🏛️ بیمه اتکایی رایا 📋 مشخصات کمیته ریسک 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۵۳:۳۵ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 23 views 05:24 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #نیشکر 🏛️ توسعه نیشکر و صنایع جانبی ان 📌 #گزارش_فعالیت_ماهانه_دوره_۱_ماهه 📋 گزارش فعالیت ماهانه دوره ۱ ماهه منتهی به ۱۴۰۵/۰۶/۳۱(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۰۸:۵۴:۴۱ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 27 views 05:27 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/codalboursetrader/247619</t>
+          <t>https://t.me/codalboursetrader/247620</t>
         </is>
       </c>
     </row>
@@ -17082,7 +16846,7 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="48" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -17135,7 +16899,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>4 آسود نهال آرمان اقتصاد لینک سابقه معاملات آسود ریز معاملات امروز آسود سهامداران عمده آسود افزایش سرمایه آسود تعدیل قیمت آسود تابلو عرضه و تقاضا صورتهای مالی نسبتهای مالی رتبه بندی بنیادی آسود اندیکاتورها آسود در TSETMC آسود در کدال</t>
+          <t>آسود در کدال</t>
         </is>
       </c>
     </row>
@@ -17162,24 +16926,24 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2 واتی گروه سرمایه گذاری آتیه دماوند لینک سابقه معاملات واتی ریز معاملات امروز واتی سهامداران عمده واتی افزایش سرمایه واتی تعدیل قیمت واتی تابلو عرضه و تقاضا صورتهای مالی نسبتهای مالی رتبه بندی بنیادی واتی اندیکاتورها واتی در TSETMC واتی در کدال</t>
+          <t>واتی در کدال</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ولملت</t>
+          <t>وزمین</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ولملت در کدال</t>
+          <t>وزمین در کدال</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>https://codal.ir/ReportList.aspx?search&amp;Symbol=ولملت</t>
+          <t>https://codal.ir/ReportList.aspx?search&amp;Symbol=وزمین</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -17189,7 +16953,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5 ولملت واسپاری ملت لینک سابقه معاملات ولملت ریز معاملات امروز ولملت سهامداران عمده ولملت افزایش سرمایه ولملت تعدیل قیمت ولملت تابلو عرضه و تقاضا صورتهای مالی نسبتهای مالی رتبه بندی بنیادی ولملت اندیکاتورها ولملت در TSETMC ولملت در کدال</t>
+          <t>وزمین در کدال</t>
         </is>
       </c>
     </row>
@@ -17216,7 +16980,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3 پاسا ایران یاسا تایر و رابر لینک سابقه معاملات پاسا ریز معاملات امروز پاسا سهامداران عمده پاسا افزایش سرمایه پاسا تعدیل قیمت پاسا تابلو عرضه و تقاضا صورتهای مالی نسبتهای مالی رتبه بندی بنیادی پاسا اندیکاتورها پاسا در TSETMC پاسا در کدال</t>
+          <t>پاسا در کدال</t>
         </is>
       </c>
     </row>
@@ -17232,12 +16996,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
@@ -17302,7 +17066,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>https://excel.codal.ir/service/Excel/GetAll/J1aPpo73eSoo2Dong5HGyg%3d%3d/0</t>
+          <t>https://excel.codal.ir/service/Excel/GetAll/JBsqvslfTvARtL61f2Wg9w%3d%3d/0</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -17312,7 +17076,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>000		https://excel.codal.ir/service/Excel/GetAll/JBsqvslfTvARtL61f2Wg9w%3d%3d/0</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
@@ -17338,19 +17102,19 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>URLError: &lt;urlopen error timed out&gt;</t>
+          <t>curl: (28) Failed to connect to excel.codal.ir port 443 after 7000 ms: Timeout was reached</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>تلگرام بورس‌تریدر</t>
+          <t>بورس‌تریدر</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>https://excel.codal.ir/service/Excel/GetAll/r2RrHefXhTNZFw8HmjCTZQ%3d%3d/0</t>
+          <t>https://excel.codal.ir/service/Excel/GetAll/J1aPpo73eSoo2Dong5HGyg%3d%3d/0</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -17360,7 +17124,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>000		https://excel.codal.ir/service/Excel/GetAll/J1aPpo73eSoo2Dong5HGyg%3d%3d/0</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
@@ -17386,7 +17150,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>URLError: &lt;urlopen error timed out&gt;</t>
+          <t>curl: (28) Failed to connect to excel.codal.ir port 443 after 7000 ms: Timeout was reached</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -17398,7 +17162,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>https://excel.codal.ir/service/Excel/GetAll/AhmPLM0rSuvgMOOObOOOkQQQaQQQKkQJrQ%3d%3d/0</t>
+          <t>https://excel.codal.ir/service/Excel/GetAll/r2RrHefXhTNZFw8HmjCTZQ%3d%3d/0</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -17408,7 +17172,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>000		https://excel.codal.ir/service/Excel/GetAll/r2RrHefXhTNZFw8HmjCTZQ%3d%3d/0</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
@@ -17434,7 +17198,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>URLError: &lt;urlopen error timed out&gt;</t>
+          <t>curl: (28) Failed to connect to excel.codal.ir port 443 after 7000 ms: Timeout was reached</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -17444,19 +17208,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>https://excel.codal.ir/service/Excel/GetAll/cr2KkEseV1SvOu3ZCycmug%3d%3d/0</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>excel.codal.ir</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
@@ -17482,245 +17238,13 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>URLError: &lt;urlopen error timed out&gt;</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>تلگرام بورس‌تریدر</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>https://excel.codal.ir/service/Excel/GetAll/p3YYElxIlOXNpKcxvKb4kw%3d%3d/0</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>excel.codal.ir</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>خیر/تأییدنشده</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>URLError: &lt;urlopen error timed out&gt;</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>تلگرام بورس‌تریدر</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>https://excel.codal.ir/service/Excel/GetAll/MnQQQaQQQqAa9B8Hcrzvj1xCh2KA%3d%3d/0</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>excel.codal.ir</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>خیر/تأییدنشده</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>URLError: &lt;urlopen error timed out&gt;</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>تلگرام بورس‌تریدر</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>https://excel.codal.ir/service/Excel/GetAll/sY2QQQaQQQyZjTd77yEfU0Zfo64A%3d%3d/0</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>excel.codal.ir</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>خیر/تأییدنشده</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>URLError: &lt;urlopen error timed out&gt;</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>تلگرام بورس‌تریدر</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>https://excel.codal.ir/service/Excel/GetAll/UvIWOOObOOO0tMGKySDxDoDQQQaQQQJKTw%3d%3d/0</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>excel.codal.ir</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>خیر/تأییدنشده</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>URLError: &lt;urlopen error timed out&gt;</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>تلگرام بورس‌تریدر</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>خیر/تأییدنشده</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24 پیوست دیگر برای محدودکردن زمان اجرا آزمایش نشد.</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr"/>
+          <t>33 پیوست دیگر برای محدودکردن زمان اجرا آزمایش نشد.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J10"/>
+  <autoFilter ref="A1:J5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17773,16 +17297,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -17845,7 +17369,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>243602</t>
+          <t>243786</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -17878,7 +17402,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>159319</t>
+          <t>159651</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -17896,7 +17420,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/s/codalboursetrader?before=247746</t>
+          <t>https://t.me/s/codalboursetrader?before=247747</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -17911,7 +17435,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>154626</t>
+          <t>156543</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -17929,7 +17453,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/s/codalboursetrader?before=247725</t>
+          <t>https://t.me/s/codalboursetrader?before=247726</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -17944,7 +17468,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>158752</t>
+          <t>157998</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -17962,7 +17486,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/s/codalboursetrader?before=247704</t>
+          <t>https://t.me/s/codalboursetrader?before=247705</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -17977,7 +17501,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>155692</t>
+          <t>157131</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -17995,7 +17519,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/s/codalboursetrader?before=247683</t>
+          <t>https://t.me/s/codalboursetrader?before=247684</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -18010,7 +17534,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>156518</t>
+          <t>156459</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -18028,7 +17552,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/s/codalboursetrader?before=247662</t>
+          <t>https://t.me/s/codalboursetrader?before=247663</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -18043,7 +17567,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>156454</t>
+          <t>157437</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -18061,7 +17585,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/s/codalboursetrader?before=247641</t>
+          <t>https://t.me/s/codalboursetrader?before=247642</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -18076,7 +17600,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>161675</t>
+          <t>162019</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -18094,7 +17618,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/s/codalboursetrader?before=247620</t>
+          <t>https://t.me/s/codalboursetrader?before=247621</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -18109,7 +17633,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>166905</t>
+          <t>168504</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -18127,12 +17651,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>https://excel.codal.ir/service/Excel/GetAll/J1aPpo73eSoo2Dong5HGyg%3d%3d/0</t>
+          <t>https://excel.codal.ir/service/Excel/GetAll/JBsqvslfTvARtL61f2Wg9w%3d%3d/0</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>000		https://excel.codal.ir/service/Excel/GetAll/JBsqvslfTvARtL61f2Wg9w%3d%3d/0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
@@ -18148,7 +17672,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>URLError: &lt;urlopen error timed out&gt;</t>
+          <t>curl: (28) Failed to connect to excel.codal.ir port 443 after 7000 ms: Timeout was reached</t>
         </is>
       </c>
     </row>
@@ -18160,12 +17684,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>https://excel.codal.ir/service/Excel/GetAll/r2RrHefXhTNZFw8HmjCTZQ%3d%3d/0</t>
+          <t>https://excel.codal.ir/service/Excel/GetAll/J1aPpo73eSoo2Dong5HGyg%3d%3d/0</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>000		https://excel.codal.ir/service/Excel/GetAll/J1aPpo73eSoo2Dong5HGyg%3d%3d/0</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
@@ -18181,7 +17705,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>URLError: &lt;urlopen error timed out&gt;</t>
+          <t>curl: (28) Failed to connect to excel.codal.ir port 443 after 7000 ms: Timeout was reached</t>
         </is>
       </c>
     </row>
@@ -18193,12 +17717,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>https://excel.codal.ir/service/Excel/GetAll/AhmPLM0rSuvgMOOObOOOkQQQaQQQKkQJrQ%3d%3d/0</t>
+          <t>https://excel.codal.ir/service/Excel/GetAll/r2RrHefXhTNZFw8HmjCTZQ%3d%3d/0</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>000		https://excel.codal.ir/service/Excel/GetAll/r2RrHefXhTNZFw8HmjCTZQ%3d%3d/0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr"/>
@@ -18214,177 +17738,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>URLError: &lt;urlopen error timed out&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>پیوست اکسل</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>https://excel.codal.ir/service/Excel/GetAll/cr2KkEseV1SvOu3ZCycmug%3d%3d/0</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>URLError: &lt;urlopen error timed out&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>پیوست اکسل</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>https://excel.codal.ir/service/Excel/GetAll/p3YYElxIlOXNpKcxvKb4kw%3d%3d/0</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>URLError: &lt;urlopen error timed out&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>پیوست اکسل</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>https://excel.codal.ir/service/Excel/GetAll/MnQQQaQQQqAa9B8Hcrzvj1xCh2KA%3d%3d/0</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>URLError: &lt;urlopen error timed out&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>پیوست اکسل</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>https://excel.codal.ir/service/Excel/GetAll/sY2QQQaQQQyZjTd77yEfU0Zfo64A%3d%3d/0</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>URLError: &lt;urlopen error timed out&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>پیوست اکسل</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>https://excel.codal.ir/service/Excel/GetAll/UvIWOOObOOO0tMGKySDxDoDQQQaQQQJKTw%3d%3d/0</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>URLError: &lt;urlopen error timed out&gt;</t>
+          <t>curl: (28) Failed to connect to excel.codal.ir port 443 after 7000 ms: Timeout was reached</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G18"/>
+  <autoFilter ref="A1:G13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/codal_disclosures_latest.xlsx
+++ b/data/codal_disclosures_latest.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13T13:27:49+00:00</t>
+          <t>2026-10-13T13:29:16+00:00</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -797,7 +797,7 @@
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پارند_ثابت 🏛️ صندوق سرمایه گذاری پارند پایدار سپهر(ETF) 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۴۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 4 views 13:18 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پارند_ثابت 🏛️ صندوق سرمایه گذاری پارند پایدار سپهر(ETF) 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۴۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 5 views 13:18 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پاسا 🏛️ ایران یاسا تایر و رابر 📋 مشخصات کمیته ریسک 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۳۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 4 views 13:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پاسا 🏛️ ایران یاسا تایر و رابر 📋 مشخصات کمیته ریسک 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۳۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 5 views 13:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -897,7 +897,7 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ولملت 🏛️ واسپاری ملت 📋 توقف نماد معاملاتی ناشر به استناد ماده ۱۹ مکرر/ ۱۲ مکرر ۳دستورالعمل اجرایی نحوه انجام معاملات 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۲:۳۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 5 views 13:15 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ولملت 🏛️ واسپاری ملت 📋 توقف نماد معاملاتی ناشر به استناد ماده ۱۹ مکرر/ ۱۲ مکرر ۳دستورالعمل اجرایی نحوه انجام معاملات 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۲:۳۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 6 views 13:15 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پاسا 🏛️ ایران یاسا تایر و رابر 📋 کمیته انتصابات 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۲:۲۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 5 views 13:15 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پاسا 🏛️ ایران یاسا تایر و رابر 📋 کمیته انتصابات 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۲:۲۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 6 views 13:15 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کفرآور 🏛️ فرآورده های سیمان شرق 📌 #گزارش_فعالیت_هیئت_مدیره 📋 گزارش فعالیت هیئت مدیره دوره ۱۲ ماهه منتهی به ۱۴۰۵/۰۵/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۲۶:۴۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 11 views 12:57 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کفرآور 🏛️ فرآورده های سیمان شرق 📌 #گزارش_فعالیت_هیئت_مدیره 📋 گزارش فعالیت هیئت مدیره دوره ۱۲ ماهه منتهی به ۱۴۰۵/۰۵/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۲۶:۴۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 12:57 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1409,7 +1409,7 @@
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 توضیحات در خصوص اطلاعات و صورت های مالی منتشر شده 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۲۴:۴۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 11 views 12:57 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 توضیحات در خصوص اطلاعات و صورت های مالی منتشر شده 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۲۴:۴۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 12:57 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تپسی 🏛️ پیشگامان فن آوری و دانش آرامیس 📌 #مشخصات_کمیته_حسابرسی_و_واحد_حسابرسی_داخلی 📋 مشخصات کمیته حسابرسی و واحد حسابرسی داخلی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۲۲:۳۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 11 views 12:54 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تپسی 🏛️ پیشگامان فن آوری و دانش آرامیس 📌 #مشخصات_کمیته_حسابرسی_و_واحد_حسابرسی_داخلی 📋 مشخصات کمیته حسابرسی و واحد حسابرسی داخلی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۲۲:۳۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 12:54 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شپترو 🏛️ پتروشیمی آبادان 📋 مشخصات کمیته ریسک 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۳۵:۱۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 12:06 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شپترو 🏛️ پتروشیمی آبادان 📋 مشخصات کمیته ریسک 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۳۵:۱۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 14 views 12:06 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2571,7 +2571,7 @@
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #فافق 🏛️ صنایع مس افق کرمان 📌 #معرفی /تغییر_در_ترکیب_اعضای_هیئت _مدیره 📋 معرفی /تغییر در ترکیب اعضای هیئت مدیره/مدیر عامل(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۱۴:۱۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 9 views 11:45 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #فافق 🏛️ صنایع مس افق کرمان 📌 #معرفی /تغییر_در_ترکیب_اعضای_هیئت _مدیره 📋 معرفی /تغییر در ترکیب اعضای هیئت مدیره/مدیر عامل(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۱۴:۱۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 10 views 11:45 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8807,7 +8807,7 @@
       <c r="H159" s="2" t="inlineStr"/>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #واتی 🏛️ گروه سرمایه گذاری آتیه دماوند 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (برگزاری مزایده - گروه ب) منتهی به سال مالی ۱۴۰۵/۰۹/۳۰ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۳۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 4 views 13:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #واتی 🏛️ گروه سرمایه گذاری آتیه دماوند 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (برگزاری مزایده - گروه ب) منتهی به سال مالی ۱۴۰۵/۰۹/۳۰ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۳۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 5 views 13:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       <c r="H161" s="2" t="inlineStr"/>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آسود 🏛️ نهال آرمان اقتصاد 📋 صورت وضعیت پورتفوی صندوق سرمایه گذاری دوره ۱ ماهه منتهی به ۱۴۰۵/۰۷/۱۵ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۳:۵۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 4 views 13:15 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آسود 🏛️ نهال آرمان اقتصاد 📋 صورت وضعیت پورتفوی صندوق سرمایه گذاری دوره ۱ ماهه منتهی به ۱۴۰۵/۰۷/۱۵ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۳:۵۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 5 views 13:15 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
@@ -8953,7 +8953,7 @@
       <c r="H162" s="2" t="inlineStr"/>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #وزمین 🏛️ بانک ایران زمین 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) (شرکت توسعه تجارت داتام) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۵۴:۴۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 1 view 13:27 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #وزمین 🏛️ بانک ایران زمین 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) (شرکت توسعه تجارت داتام) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۵۴:۴۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 3 views 13:27 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -9511,7 +9511,7 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 توضیحات در خصوص اطلاعات و صورت های مالی منتشر شده 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۲۴:۴۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 11 views 12:57 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 توضیحات در خصوص اطلاعات و صورت های مالی منتشر شده 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۲۴:۴۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 12:57 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11459,7 +11459,7 @@
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #وزمین 🏛️ بانک ایران زمین 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) (شرکت توسعه تجارت داتام) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۵۴:۴۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 1 view 13:27 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #وزمین 🏛️ بانک ایران زمین 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) (شرکت توسعه تجارت داتام) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۵۴:۴۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 3 views 13:27 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11662,7 +11662,7 @@
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تپسی 🏛️ پیشگامان فن آوری و دانش آرامیس 📌 #مشخصات_کمیته_حسابرسی_و_واحد_حسابرسی_داخلی 📋 مشخصات کمیته حسابرسی و واحد حسابرسی داخلی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۲۲:۳۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 11 views 12:54 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #تپسی 🏛️ پیشگامان فن آوری و دانش آرامیس 📌 #مشخصات_کمیته_حسابرسی_و_واحد_حسابرسی_داخلی 📋 مشخصات کمیته حسابرسی و واحد حسابرسی داخلی 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۲۲:۳۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 12:54 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11695,7 +11695,7 @@
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 توضیحات در خصوص اطلاعات و صورت های مالی منتشر شده 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۲۴:۴۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 11 views 12:57 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پیمان 🏛️ پیمان غرب 📌 #توضیحات_در_خصوص_اطلاعات_و_صورت_های_مالی_منتشر_شده 📋 توضیحات در خصوص اطلاعات و صورت های مالی منتشر شده 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۲۴:۴۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 12:57 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11728,7 +11728,7 @@
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کفرآور 🏛️ فرآورده های سیمان شرق 📌 #گزارش_فعالیت_هیئت_مدیره 📋 گزارش فعالیت هیئت مدیره دوره ۱۲ ماهه منتهی به ۱۴۰۵/۰۵/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۲۶:۴۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 11 views 12:57 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #کفرآور 🏛️ فرآورده های سیمان شرق 📌 #گزارش_فعالیت_هیئت_مدیره 📋 گزارش فعالیت هیئت مدیره دوره ۱۲ ماهه منتهی به ۱۴۰۵/۰۵/۳۱ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۲۶:۴۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 12 views 12:57 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11992,7 +11992,7 @@
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پاسا 🏛️ ایران یاسا تایر و رابر 📋 کمیته انتصابات 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۲:۲۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 5 views 13:15 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پاسا 🏛️ ایران یاسا تایر و رابر 📋 کمیته انتصابات 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۲:۲۴ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 6 views 13:15 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12025,7 +12025,7 @@
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ولملت 🏛️ واسپاری ملت 📋 توقف نماد معاملاتی ناشر به استناد ماده ۱۹ مکرر/ ۱۲ مکرر ۳دستورالعمل اجرایی نحوه انجام معاملات 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۲:۳۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 5 views 13:15 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #ولملت 🏛️ واسپاری ملت 📋 توقف نماد معاملاتی ناشر به استناد ماده ۱۹ مکرر/ ۱۲ مکرر ۳دستورالعمل اجرایی نحوه انجام معاملات 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۲:۳۰ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 6 views 13:15 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12058,7 +12058,7 @@
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آسود 🏛️ نهال آرمان اقتصاد 📋 صورت وضعیت پورتفوی صندوق سرمایه گذاری دوره ۱ ماهه منتهی به ۱۴۰۵/۰۷/۱۵ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۳:۵۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 4 views 13:15 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #آسود 🏛️ نهال آرمان اقتصاد 📋 صورت وضعیت پورتفوی صندوق سرمایه گذاری دوره ۱ ماهه منتهی به ۱۴۰۵/۰۷/۱۵ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۳:۵۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 5 views 13:15 📋 اطلاعیه 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12091,7 +12091,7 @@
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پاسا 🏛️ ایران یاسا تایر و رابر 📋 مشخصات کمیته ریسک 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۳۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 4 views 13:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پاسا 🏛️ ایران یاسا تایر و رابر 📋 مشخصات کمیته ریسک 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۳۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 5 views 13:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12124,7 +12124,7 @@
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #واتی 🏛️ گروه سرمایه گذاری آتیه دماوند 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (برگزاری مزایده - گروه ب) منتهی به سال مالی ۱۴۰۵/۰۹/۳۰ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۳۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 4 views 13:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #واتی 🏛️ گروه سرمایه گذاری آتیه دماوند 📌 #افشای_اطلاعات_با_اهمیت 📋 افشای اطلاعات بااهمیت - (برگزاری مزایده - گروه ب) منتهی به سال مالی ۱۴۰۵/۰۹/۳۰ 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۳۸ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 5 views 13:18 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12157,7 +12157,7 @@
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پارند_ثابت 🏛️ صندوق سرمایه گذاری پارند پایدار سپهر(ETF) 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۴۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 4 views 13:18 📋 اطلاعیه 📕 PDF</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #پارند_ثابت 🏛️ صندوق سرمایه گذاری پارند پایدار سپهر(ETF) 📋 تصمیمات مجمع صندوق سرمایه گذاری 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۴۵:۴۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 5 views 13:18 📋 اطلاعیه 📕 PDF</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12190,7 +12190,7 @@
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #وزمین 🏛️ بانک ایران زمین 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) (شرکت توسعه تجارت داتام) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۵۴:۴۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 1 view 13:27 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #وزمین 🏛️ بانک ایران زمین 📌 #صورت_های_مالی_میان_دوره_ای 📋 صورت های مالی سال مالی منتهی به ۱۴۰۴/۱۲/۲۹ (حسابرسی شده) (شرکت توسعه تجارت داتام) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۶:۵۴:۴۲ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 3 views 13:27 📋 اطلاعیه 📕 PDF 📘 Excel 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12256,7 +12256,7 @@
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #فافق 🏛️ صنایع مس افق کرمان 📌 #معرفی /تغییر_در_ترکیب_اعضای_هیئت _مدیره 📋 معرفی /تغییر در ترکیب اعضای هیئت مدیره/مدیر عامل(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۱۴:۱۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 9 views 11:45 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #فافق 🏛️ صنایع مس افق کرمان 📌 #معرفی /تغییر_در_ترکیب_اعضای_هیئت _مدیره 📋 معرفی /تغییر در ترکیب اعضای هیئت مدیره/مدیر عامل(اصلاحیه) 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۱۴:۱۷ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 10 views 11:45 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12454,7 +12454,7 @@
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شپترو 🏛️ پتروشیمی آبادان 📋 مشخصات کمیته ریسک 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۳۵:۱۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 13 views 12:06 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
+          <t>اطلاعیه کدال | بورس تریدر 🏷️ #شپترو 🏛️ پتروشیمی آبادان 📋 مشخصات کمیته ریسک 🔗 لینک اطلاعیه 📆 ۱۴۰۵/۰۷/۲۱ ۱۵:۳۵:۱۳ ━━━━━━━━━━━━━━━ 🌐 Bourse-Trader.ir 🆔 @CodalBourseTrader 14 views 12:06 📋 اطلاعیه 📕 PDF 🔗 TSETMC 📊 سابقه 📈 چارت</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -17001,7 +17001,7 @@
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
@@ -17076,7 +17076,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>000		https://excel.codal.ir/service/Excel/GetAll/JBsqvslfTvARtL61f2Wg9w%3d%3d/0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
@@ -17102,7 +17102,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>curl: (28) Failed to connect to excel.codal.ir port 443 after 7000 ms: Timeout was reached</t>
+          <t>curl: (28) Failed to connect to excel.codal.ir port 443 after 7001 ms: Timeout was reached</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>000		https://excel.codal.ir/service/Excel/GetAll/J1aPpo73eSoo2Dong5HGyg%3d%3d/0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
@@ -17150,7 +17150,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>curl: (28) Failed to connect to excel.codal.ir port 443 after 7000 ms: Timeout was reached</t>
+          <t>curl: (28) Failed to connect to excel.codal.ir port 443 after 7001 ms: Timeout was reached</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -17172,7 +17172,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>000		https://excel.codal.ir/service/Excel/GetAll/r2RrHefXhTNZFw8HmjCTZQ%3d%3d/0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
@@ -17198,7 +17198,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>curl: (28) Failed to connect to excel.codal.ir port 443 after 7000 ms: Timeout was reached</t>
+          <t>curl: (28) Failed to connect to excel.codal.ir port 443 after 7002 ms: Timeout was reached</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -17302,7 +17302,7 @@
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>159651</t>
+          <t>159652</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -17435,7 +17435,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>156543</t>
+          <t>156546</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -17468,7 +17468,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>157998</t>
+          <t>157996</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -17501,7 +17501,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>157131</t>
+          <t>157132</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -17534,7 +17534,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>156459</t>
+          <t>156458</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -17600,7 +17600,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>162019</t>
+          <t>162016</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>168504</t>
+          <t>168505</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -17656,7 +17656,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>000		https://excel.codal.ir/service/Excel/GetAll/JBsqvslfTvARtL61f2Wg9w%3d%3d/0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>curl: (28) Failed to connect to excel.codal.ir port 443 after 7000 ms: Timeout was reached</t>
+          <t>curl: (28) Failed to connect to excel.codal.ir port 443 after 7001 ms: Timeout was reached</t>
         </is>
       </c>
     </row>
@@ -17689,7 +17689,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>000		https://excel.codal.ir/service/Excel/GetAll/J1aPpo73eSoo2Dong5HGyg%3d%3d/0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
@@ -17705,7 +17705,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>curl: (28) Failed to connect to excel.codal.ir port 443 after 7000 ms: Timeout was reached</t>
+          <t>curl: (28) Failed to connect to excel.codal.ir port 443 after 7001 ms: Timeout was reached</t>
         </is>
       </c>
     </row>
@@ -17722,7 +17722,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>000		https://excel.codal.ir/service/Excel/GetAll/r2RrHefXhTNZFw8HmjCTZQ%3d%3d/0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr"/>
@@ -17738,7 +17738,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>curl: (28) Failed to connect to excel.codal.ir port 443 after 7000 ms: Timeout was reached</t>
+          <t>curl: (28) Failed to connect to excel.codal.ir port 443 after 7002 ms: Timeout was reached</t>
         </is>
       </c>
     </row>
